--- a/research/traditional_assets/database/data/luxembourg/luxembourg_oil_gas_distribution.xlsx
+++ b/research/traditional_assets/database/data/luxembourg/luxembourg_oil_gas_distribution.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07031265058164096</v>
+        <v>0.07017106783109035</v>
       </c>
       <c r="C2">
-        <v>800.8839390433102</v>
+        <v>793.1866217941183</v>
       </c>
       <c r="D2">
-        <v>572.1839390433103</v>
+        <v>572.6236217941183</v>
       </c>
       <c r="E2">
-        <v>-315.9</v>
+        <v>-307.763</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>8.137</v>
       </c>
       <c r="G2">
         <v>228.7</v>
@@ -1445,28 +1445,28 @@
         <v>194.1</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.4092911</v>
       </c>
       <c r="N2">
-        <v>194.1</v>
+        <v>193.6907089</v>
       </c>
       <c r="O2">
-        <v>48.40854</v>
+        <v>48.30646279966</v>
       </c>
       <c r="P2">
-        <v>145.69146</v>
+        <v>145.38424610034</v>
       </c>
       <c r="Q2">
-        <v>206.29146</v>
+        <v>205.98424610034</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07031265058164096</v>
+        <v>0.0704985010415054</v>
       </c>
       <c r="T2">
-        <v>0.5661120226706919</v>
+        <v>0.5704041810971224</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>474.2345973318257</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07017106783109035</v>
+        <v>0.07002948508053974</v>
       </c>
       <c r="C3">
-        <v>793.1866217941183</v>
+        <v>785.4899807945579</v>
       </c>
       <c r="D3">
-        <v>572.6236217941183</v>
+        <v>573.063980794558</v>
       </c>
       <c r="E3">
-        <v>-307.763</v>
+        <v>-299.626</v>
       </c>
       <c r="F3">
-        <v>8.137</v>
+        <v>16.274</v>
       </c>
       <c r="G3">
         <v>228.7</v>
@@ -1527,28 +1527,28 @@
         <v>194.1</v>
       </c>
       <c r="M3">
-        <v>0.4092911</v>
+        <v>0.8185822</v>
       </c>
       <c r="N3">
-        <v>193.6907089</v>
+        <v>193.2814178</v>
       </c>
       <c r="O3">
-        <v>48.30646279966</v>
+        <v>48.20438559932</v>
       </c>
       <c r="P3">
-        <v>145.38424610034</v>
+        <v>145.07703220068</v>
       </c>
       <c r="Q3">
-        <v>205.98424610034</v>
+        <v>205.67703220068</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.0704985010415054</v>
+        <v>0.07068814436789769</v>
       </c>
       <c r="T3">
-        <v>0.5704041810971224</v>
+        <v>0.5747839345934801</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>474.2345973318257</v>
+        <v>237.1172986659128</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07002948508053974</v>
+        <v>0.06988790232998912</v>
       </c>
       <c r="C4">
-        <v>785.4899807945579</v>
+        <v>777.7940176059785</v>
       </c>
       <c r="D4">
-        <v>573.063980794558</v>
+        <v>573.5050176059787</v>
       </c>
       <c r="E4">
-        <v>-299.626</v>
+        <v>-291.489</v>
       </c>
       <c r="F4">
-        <v>16.274</v>
+        <v>24.411</v>
       </c>
       <c r="G4">
         <v>228.7</v>
@@ -1609,28 +1609,28 @@
         <v>194.1</v>
       </c>
       <c r="M4">
-        <v>0.8185822</v>
+        <v>1.2278733</v>
       </c>
       <c r="N4">
-        <v>193.2814178</v>
+        <v>192.8721267</v>
       </c>
       <c r="O4">
-        <v>48.20438559932</v>
+        <v>48.10230839898</v>
       </c>
       <c r="P4">
-        <v>145.07703220068</v>
+        <v>144.76981830102</v>
       </c>
       <c r="Q4">
-        <v>205.67703220068</v>
+        <v>205.36981830102</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07068814436789769</v>
+        <v>0.07088169786596817</v>
       </c>
       <c r="T4">
-        <v>0.5747839345934801</v>
+        <v>0.5792539922856389</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>237.1172986659128</v>
+        <v>158.0781991106086</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.06988790232998912</v>
+        <v>0.06974631957943851</v>
       </c>
       <c r="C5">
-        <v>777.7940176059785</v>
+        <v>770.0987337945394</v>
       </c>
       <c r="D5">
-        <v>573.5050176059787</v>
+        <v>573.9467337945393</v>
       </c>
       <c r="E5">
-        <v>-291.489</v>
+        <v>-283.352</v>
       </c>
       <c r="F5">
-        <v>24.411</v>
+        <v>32.548</v>
       </c>
       <c r="G5">
         <v>228.7</v>
@@ -1691,28 +1691,28 @@
         <v>194.1</v>
       </c>
       <c r="M5">
-        <v>1.2278733</v>
+        <v>1.6371644</v>
       </c>
       <c r="N5">
-        <v>192.8721267</v>
+        <v>192.4628356</v>
       </c>
       <c r="O5">
-        <v>48.10230839898</v>
+        <v>48.00023119864</v>
       </c>
       <c r="P5">
-        <v>144.76981830102</v>
+        <v>144.46260440136</v>
       </c>
       <c r="Q5">
-        <v>205.36981830102</v>
+        <v>205.06260440136</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07088169786596817</v>
+        <v>0.07107928372858179</v>
       </c>
       <c r="T5">
-        <v>0.5792539922856389</v>
+        <v>0.5838171761797178</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>158.0781991106086</v>
+        <v>118.5586493329564</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.06974631957943851</v>
+        <v>0.0696047368288879</v>
       </c>
       <c r="C6">
-        <v>770.0987337945394</v>
+        <v>762.4041309312283</v>
       </c>
       <c r="D6">
-        <v>573.9467337945393</v>
+        <v>574.3891309312282</v>
       </c>
       <c r="E6">
-        <v>-283.352</v>
+        <v>-275.215</v>
       </c>
       <c r="F6">
-        <v>32.548</v>
+        <v>40.685</v>
       </c>
       <c r="G6">
         <v>228.7</v>
@@ -1773,28 +1773,28 @@
         <v>194.1</v>
       </c>
       <c r="M6">
-        <v>1.6371644</v>
+        <v>2.0464555</v>
       </c>
       <c r="N6">
-        <v>192.4628356</v>
+        <v>192.0535445</v>
       </c>
       <c r="O6">
-        <v>48.00023119864</v>
+        <v>47.8981539983</v>
       </c>
       <c r="P6">
-        <v>144.46260440136</v>
+        <v>144.1553905017</v>
       </c>
       <c r="Q6">
-        <v>205.06260440136</v>
+        <v>204.7553905017</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07107928372858179</v>
+        <v>0.07128102929356621</v>
       </c>
       <c r="T6">
-        <v>0.5838171761797178</v>
+        <v>0.5884764271031456</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>118.5586493329564</v>
+        <v>94.84691946636514</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0696047368288879</v>
+        <v>0.06946315407833728</v>
       </c>
       <c r="C7">
-        <v>762.4041309312283</v>
+        <v>754.7102105918808</v>
       </c>
       <c r="D7">
-        <v>574.3891309312282</v>
+        <v>574.8322105918809</v>
       </c>
       <c r="E7">
-        <v>-275.215</v>
+        <v>-267.078</v>
       </c>
       <c r="F7">
-        <v>40.685</v>
+        <v>48.82200000000001</v>
       </c>
       <c r="G7">
         <v>228.7</v>
@@ -1855,28 +1855,28 @@
         <v>194.1</v>
       </c>
       <c r="M7">
-        <v>2.0464555</v>
+        <v>2.4557466</v>
       </c>
       <c r="N7">
-        <v>192.0535445</v>
+        <v>191.6442534</v>
       </c>
       <c r="O7">
-        <v>47.8981539983</v>
+        <v>47.79607679796</v>
       </c>
       <c r="P7">
-        <v>144.1553905017</v>
+        <v>143.84817660204</v>
       </c>
       <c r="Q7">
-        <v>204.7553905017</v>
+        <v>204.44817660204</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07128102929356621</v>
+        <v>0.07148706731738008</v>
       </c>
       <c r="T7">
-        <v>0.5884764271031456</v>
+        <v>0.5932348110249444</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>94.84691946636514</v>
+        <v>79.03909955530428</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.06946315407833728</v>
+        <v>0.06932157132778669</v>
       </c>
       <c r="C8">
-        <v>754.7102105918808</v>
+        <v>747.016974357199</v>
       </c>
       <c r="D8">
-        <v>574.8322105918809</v>
+        <v>575.2759743571989</v>
       </c>
       <c r="E8">
-        <v>-267.078</v>
+        <v>-258.941</v>
       </c>
       <c r="F8">
-        <v>48.822</v>
+        <v>56.959</v>
       </c>
       <c r="G8">
         <v>228.7</v>
@@ -1937,28 +1937,28 @@
         <v>194.1</v>
       </c>
       <c r="M8">
-        <v>2.4557466</v>
+        <v>2.8650377</v>
       </c>
       <c r="N8">
-        <v>191.6442534</v>
+        <v>191.2349623</v>
       </c>
       <c r="O8">
-        <v>47.79607679796</v>
+        <v>47.69399959762001</v>
       </c>
       <c r="P8">
-        <v>143.84817660204</v>
+        <v>143.54096270238</v>
       </c>
       <c r="Q8">
-        <v>204.44817660204</v>
+        <v>204.14096270238</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07148706731738008</v>
+        <v>0.07169753626643728</v>
       </c>
       <c r="T8">
-        <v>0.5932348110249444</v>
+        <v>0.598095525783771</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>79.03909955530429</v>
+        <v>67.74779961883225</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.06932157132778667</v>
+        <v>0.06917998857723606</v>
       </c>
       <c r="C9">
-        <v>747.0169743571989</v>
+        <v>739.3244238127691</v>
       </c>
       <c r="D9">
-        <v>575.2759743571989</v>
+        <v>575.720423812769</v>
       </c>
       <c r="E9">
-        <v>-258.941</v>
+        <v>-250.804</v>
       </c>
       <c r="F9">
-        <v>56.95900000000001</v>
+        <v>65.096</v>
       </c>
       <c r="G9">
         <v>228.7</v>
@@ -2019,28 +2019,28 @@
         <v>194.1</v>
       </c>
       <c r="M9">
-        <v>2.8650377</v>
+        <v>3.2743288</v>
       </c>
       <c r="N9">
-        <v>191.2349623</v>
+        <v>190.8256712</v>
       </c>
       <c r="O9">
-        <v>47.69399959762001</v>
+        <v>47.59192239728</v>
       </c>
       <c r="P9">
-        <v>143.54096270238</v>
+        <v>143.23374880272</v>
       </c>
       <c r="Q9">
-        <v>204.14096270238</v>
+        <v>203.83374880272</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07169753626643728</v>
+        <v>0.0719125806274305</v>
       </c>
       <c r="T9">
-        <v>0.598095525783771</v>
+        <v>0.603061908254746</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>67.74779961883223</v>
+        <v>59.2793246664782</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.06917998857723606</v>
+        <v>0.06903840582668545</v>
       </c>
       <c r="C10">
-        <v>739.3244238127691</v>
+        <v>731.6325605490813</v>
       </c>
       <c r="D10">
-        <v>575.720423812769</v>
+        <v>576.1655605490813</v>
       </c>
       <c r="E10">
-        <v>-250.804</v>
+        <v>-242.667</v>
       </c>
       <c r="F10">
-        <v>65.096</v>
+        <v>73.233</v>
       </c>
       <c r="G10">
         <v>228.7</v>
@@ -2101,28 +2101,28 @@
         <v>194.1</v>
       </c>
       <c r="M10">
-        <v>3.2743288</v>
+        <v>3.6836199</v>
       </c>
       <c r="N10">
-        <v>190.8256712</v>
+        <v>190.4163801</v>
       </c>
       <c r="O10">
-        <v>47.59192239728</v>
+        <v>47.48984519694</v>
       </c>
       <c r="P10">
-        <v>143.23374880272</v>
+        <v>142.92653490306</v>
       </c>
       <c r="Q10">
-        <v>203.83374880272</v>
+        <v>203.52653490306</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.0719125806274305</v>
+        <v>0.07213235123811587</v>
       </c>
       <c r="T10">
-        <v>0.603061908254746</v>
+        <v>0.6081374419888194</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>59.2793246664782</v>
+        <v>52.69273303686952</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.06903840582668545</v>
+        <v>0.06889682307613483</v>
       </c>
       <c r="C11">
-        <v>731.6325605490813</v>
+        <v>723.9413861615491</v>
       </c>
       <c r="D11">
-        <v>576.1655605490813</v>
+        <v>576.611386161549</v>
       </c>
       <c r="E11">
-        <v>-242.667</v>
+        <v>-234.53</v>
       </c>
       <c r="F11">
-        <v>73.233</v>
+        <v>81.37</v>
       </c>
       <c r="G11">
         <v>228.7</v>
@@ -2183,28 +2183,28 @@
         <v>194.1</v>
       </c>
       <c r="M11">
-        <v>3.6836199</v>
+        <v>4.092911</v>
       </c>
       <c r="N11">
-        <v>190.4163801</v>
+        <v>190.007089</v>
       </c>
       <c r="O11">
-        <v>47.48984519694</v>
+        <v>47.3877679966</v>
       </c>
       <c r="P11">
-        <v>142.92653490306</v>
+        <v>142.6193210034</v>
       </c>
       <c r="Q11">
-        <v>203.52653490306</v>
+        <v>203.2193210034</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07213235123811587</v>
+        <v>0.07235700564014981</v>
       </c>
       <c r="T11">
-        <v>0.6081374419888194</v>
+        <v>0.6133257653614276</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>52.69273303686952</v>
+        <v>47.42345973318257</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.06889682307613483</v>
+        <v>0.06875524032558422</v>
       </c>
       <c r="C12">
-        <v>723.9413861615491</v>
+        <v>716.2509022505269</v>
       </c>
       <c r="D12">
-        <v>576.611386161549</v>
+        <v>577.057902250527</v>
       </c>
       <c r="E12">
-        <v>-234.53</v>
+        <v>-226.393</v>
       </c>
       <c r="F12">
-        <v>81.37</v>
+        <v>89.50700000000001</v>
       </c>
       <c r="G12">
         <v>228.7</v>
@@ -2265,28 +2265,28 @@
         <v>194.1</v>
       </c>
       <c r="M12">
-        <v>4.092911</v>
+        <v>4.5022021</v>
       </c>
       <c r="N12">
-        <v>190.007089</v>
+        <v>189.5977979</v>
       </c>
       <c r="O12">
-        <v>47.3877679966</v>
+        <v>47.28569079626</v>
       </c>
       <c r="P12">
-        <v>142.6193210034</v>
+        <v>142.31210710374</v>
       </c>
       <c r="Q12">
-        <v>203.2193210034</v>
+        <v>202.91210710374</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07235700564014981</v>
+        <v>0.07258670845571261</v>
       </c>
       <c r="T12">
-        <v>0.6133257653614276</v>
+        <v>0.6186306802704991</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>47.42345973318257</v>
+        <v>43.11223612107506</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.06875524032558422</v>
+        <v>0.0686136575750336</v>
       </c>
       <c r="C13">
-        <v>716.2509022505269</v>
+        <v>708.561110421331</v>
       </c>
       <c r="D13">
-        <v>577.057902250527</v>
+        <v>577.5051104213311</v>
       </c>
       <c r="E13">
-        <v>-226.393</v>
+        <v>-218.256</v>
       </c>
       <c r="F13">
-        <v>89.50700000000001</v>
+        <v>97.64400000000001</v>
       </c>
       <c r="G13">
         <v>228.7</v>
@@ -2347,28 +2347,28 @@
         <v>194.1</v>
       </c>
       <c r="M13">
-        <v>4.5022021</v>
+        <v>4.9114932</v>
       </c>
       <c r="N13">
-        <v>189.5977979</v>
+        <v>189.1885068</v>
       </c>
       <c r="O13">
-        <v>47.28569079626</v>
+        <v>47.18361359592</v>
       </c>
       <c r="P13">
-        <v>142.31210710374</v>
+        <v>142.00489320408</v>
       </c>
       <c r="Q13">
-        <v>202.91210710374</v>
+        <v>202.60489320408</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07258670845571261</v>
+        <v>0.07282163178981091</v>
       </c>
       <c r="T13">
-        <v>0.6186306802704991</v>
+        <v>0.6240561614275039</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>43.11223612107506</v>
+        <v>39.51954977765214</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0686136575750336</v>
+        <v>0.06847207482448299</v>
       </c>
       <c r="C14">
-        <v>708.561110421331</v>
+        <v>700.8720122842574</v>
       </c>
       <c r="D14">
-        <v>577.5051104213311</v>
+        <v>577.9530122842573</v>
       </c>
       <c r="E14">
-        <v>-218.256</v>
+        <v>-210.119</v>
       </c>
       <c r="F14">
-        <v>97.64400000000001</v>
+        <v>105.781</v>
       </c>
       <c r="G14">
         <v>228.7</v>
@@ -2429,28 +2429,28 @@
         <v>194.1</v>
       </c>
       <c r="M14">
-        <v>4.9114932</v>
+        <v>5.3207843</v>
       </c>
       <c r="N14">
-        <v>189.1885068</v>
+        <v>188.7792157</v>
       </c>
       <c r="O14">
-        <v>47.18361359592</v>
+        <v>47.08153639558</v>
       </c>
       <c r="P14">
-        <v>142.00489320408</v>
+        <v>141.69767930442</v>
       </c>
       <c r="Q14">
-        <v>202.60489320408</v>
+        <v>202.29767930442</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07282163178981091</v>
+        <v>0.07306195566032528</v>
       </c>
       <c r="T14">
-        <v>0.6240561614275039</v>
+        <v>0.6296063662892676</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>39.51954977765214</v>
+        <v>36.47958441014044</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.06847207482448299</v>
+        <v>0.06833049207393238</v>
       </c>
       <c r="C15">
-        <v>700.8720122842574</v>
+        <v>693.1836094546014</v>
       </c>
       <c r="D15">
-        <v>577.9530122842573</v>
+        <v>578.4016094546014</v>
       </c>
       <c r="E15">
-        <v>-210.119</v>
+        <v>-201.982</v>
       </c>
       <c r="F15">
-        <v>105.781</v>
+        <v>113.918</v>
       </c>
       <c r="G15">
         <v>228.7</v>
@@ -2511,28 +2511,28 @@
         <v>194.1</v>
       </c>
       <c r="M15">
-        <v>5.3207843</v>
+        <v>5.7300754</v>
       </c>
       <c r="N15">
-        <v>188.7792157</v>
+        <v>188.3699246</v>
       </c>
       <c r="O15">
-        <v>47.08153639558</v>
+        <v>46.97945919524</v>
       </c>
       <c r="P15">
-        <v>141.69767930442</v>
+        <v>141.39046540476</v>
       </c>
       <c r="Q15">
-        <v>202.29767930442</v>
+        <v>201.99046540476</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07306195566032528</v>
+        <v>0.07330786845806092</v>
       </c>
       <c r="T15">
-        <v>0.6296063662892676</v>
+        <v>0.6352856456827001</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>36.47958441014044</v>
+        <v>33.87389980941612</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.06833049207393238</v>
+        <v>0.06818890932338176</v>
       </c>
       <c r="C16">
-        <v>693.1836094546014</v>
+        <v>685.4959035526779</v>
       </c>
       <c r="D16">
-        <v>578.4016094546014</v>
+        <v>578.850903552678</v>
       </c>
       <c r="E16">
-        <v>-201.982</v>
+        <v>-193.845</v>
       </c>
       <c r="F16">
-        <v>113.918</v>
+        <v>122.055</v>
       </c>
       <c r="G16">
         <v>228.7</v>
@@ -2593,28 +2593,28 @@
         <v>194.1</v>
       </c>
       <c r="M16">
-        <v>5.7300754</v>
+        <v>6.1393665</v>
       </c>
       <c r="N16">
-        <v>188.3699246</v>
+        <v>187.9606335</v>
       </c>
       <c r="O16">
-        <v>46.97945919524</v>
+        <v>46.8773819949</v>
       </c>
       <c r="P16">
-        <v>141.39046540476</v>
+        <v>141.0832515051</v>
       </c>
       <c r="Q16">
-        <v>201.99046540476</v>
+        <v>201.6832515051</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07330786845806092</v>
+        <v>0.07355956743927267</v>
       </c>
       <c r="T16">
-        <v>0.6352856456827001</v>
+        <v>0.6410985551795074</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>33.87389980941612</v>
+        <v>31.61563982212171</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.06818890932338176</v>
+        <v>0.06804732657283116</v>
       </c>
       <c r="C17">
-        <v>685.4959035526779</v>
+        <v>677.8088962038398</v>
       </c>
       <c r="D17">
-        <v>578.850903552678</v>
+        <v>579.3008962038398</v>
       </c>
       <c r="E17">
-        <v>-193.845</v>
+        <v>-185.708</v>
       </c>
       <c r="F17">
-        <v>122.055</v>
+        <v>130.192</v>
       </c>
       <c r="G17">
         <v>228.7</v>
@@ -2675,28 +2675,28 @@
         <v>194.1</v>
       </c>
       <c r="M17">
-        <v>6.1393665</v>
+        <v>6.5486576</v>
       </c>
       <c r="N17">
-        <v>187.9606335</v>
+        <v>187.5513424</v>
       </c>
       <c r="O17">
-        <v>46.8773819949</v>
+        <v>46.77530479456</v>
       </c>
       <c r="P17">
-        <v>141.0832515051</v>
+        <v>140.77603760544</v>
       </c>
       <c r="Q17">
-        <v>201.6832515051</v>
+        <v>201.37603760544</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07355956743927267</v>
+        <v>0.07381725925337043</v>
       </c>
       <c r="T17">
-        <v>0.6410985551795074</v>
+        <v>0.6470498672833817</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>31.61563982212171</v>
+        <v>29.6396623332391</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.06804732657283116</v>
+        <v>0.06790574382228055</v>
       </c>
       <c r="C18">
-        <v>677.8088962038398</v>
+        <v>670.1225890384985</v>
       </c>
       <c r="D18">
-        <v>579.3008962038398</v>
+        <v>579.7515890384984</v>
       </c>
       <c r="E18">
-        <v>-185.708</v>
+        <v>-177.571</v>
       </c>
       <c r="F18">
-        <v>130.192</v>
+        <v>138.329</v>
       </c>
       <c r="G18">
         <v>228.7</v>
@@ -2757,28 +2757,28 @@
         <v>194.1</v>
       </c>
       <c r="M18">
-        <v>6.5486576</v>
+        <v>6.9579487</v>
       </c>
       <c r="N18">
-        <v>187.5513424</v>
+        <v>187.1420513</v>
       </c>
       <c r="O18">
-        <v>46.77530479456</v>
+        <v>46.67322759422</v>
       </c>
       <c r="P18">
-        <v>140.77603760544</v>
+        <v>140.46882370578</v>
       </c>
       <c r="Q18">
-        <v>201.37603760544</v>
+        <v>201.06882370578</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07381725925337043</v>
+        <v>0.07408116050877175</v>
       </c>
       <c r="T18">
-        <v>0.6470498672833817</v>
+        <v>0.6531445844981928</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>29.6396623332391</v>
+        <v>27.89615278422504</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.06790574382228055</v>
+        <v>0.06776416107172992</v>
       </c>
       <c r="C19">
-        <v>670.1225890384985</v>
+        <v>662.4369836921422</v>
       </c>
       <c r="D19">
-        <v>579.7515890384984</v>
+        <v>580.2029836921423</v>
       </c>
       <c r="E19">
-        <v>-177.571</v>
+        <v>-169.4339999999999</v>
       </c>
       <c r="F19">
-        <v>138.329</v>
+        <v>146.466</v>
       </c>
       <c r="G19">
         <v>228.7</v>
@@ -2839,28 +2839,28 @@
         <v>194.1</v>
       </c>
       <c r="M19">
-        <v>6.9579487</v>
+        <v>7.367239800000002</v>
       </c>
       <c r="N19">
-        <v>187.1420513</v>
+        <v>186.7327602</v>
       </c>
       <c r="O19">
-        <v>46.67322759422</v>
+        <v>46.57115039388</v>
       </c>
       <c r="P19">
-        <v>140.46882370578</v>
+        <v>140.16160980612</v>
       </c>
       <c r="Q19">
-        <v>201.06882370578</v>
+        <v>200.76160980612</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07408116050877175</v>
+        <v>0.07435149838015845</v>
       </c>
       <c r="T19">
-        <v>0.6531445844981928</v>
+        <v>0.6593879533523893</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>27.89615278422504</v>
+        <v>26.34636651843475</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.06776416107172993</v>
+        <v>0.06762257832117932</v>
       </c>
       <c r="C20">
-        <v>662.4369836921422</v>
+        <v>654.7520818053579</v>
       </c>
       <c r="D20">
-        <v>580.2029836921423</v>
+        <v>580.655081805358</v>
       </c>
       <c r="E20">
-        <v>-169.434</v>
+        <v>-161.297</v>
       </c>
       <c r="F20">
-        <v>146.466</v>
+        <v>154.603</v>
       </c>
       <c r="G20">
         <v>228.7</v>
@@ -2921,28 +2921,28 @@
         <v>194.1</v>
       </c>
       <c r="M20">
-        <v>7.3672398</v>
+        <v>7.7765309</v>
       </c>
       <c r="N20">
-        <v>186.7327602</v>
+        <v>186.3234691</v>
       </c>
       <c r="O20">
-        <v>46.57115039388</v>
+        <v>46.46907319354</v>
       </c>
       <c r="P20">
-        <v>140.16160980612</v>
+        <v>139.85439590646</v>
       </c>
       <c r="Q20">
-        <v>200.76160980612</v>
+        <v>200.45439590646</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07435149838015845</v>
+        <v>0.07462851126071521</v>
       </c>
       <c r="T20">
-        <v>0.6593879533523893</v>
+        <v>0.6657854794622451</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>26.34636651843476</v>
+        <v>24.95971564904346</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.06762257832117932</v>
+        <v>0.06748099557062871</v>
       </c>
       <c r="C21">
-        <v>654.7520818053579</v>
+        <v>647.0678850238492</v>
       </c>
       <c r="D21">
-        <v>580.655081805358</v>
+        <v>581.1078850238492</v>
       </c>
       <c r="E21">
-        <v>-161.297</v>
+        <v>-153.16</v>
       </c>
       <c r="F21">
-        <v>154.603</v>
+        <v>162.74</v>
       </c>
       <c r="G21">
         <v>228.7</v>
@@ -3003,28 +3003,28 @@
         <v>194.1</v>
       </c>
       <c r="M21">
-        <v>7.7765309</v>
+        <v>8.185822</v>
       </c>
       <c r="N21">
-        <v>186.3234691</v>
+        <v>185.914178</v>
       </c>
       <c r="O21">
-        <v>46.46907319354</v>
+        <v>46.3669959932</v>
       </c>
       <c r="P21">
-        <v>139.85439590646</v>
+        <v>139.5471820068</v>
       </c>
       <c r="Q21">
-        <v>200.45439590646</v>
+        <v>200.1471820068</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07462851126071521</v>
+        <v>0.07491244946328589</v>
       </c>
       <c r="T21">
-        <v>0.6657854794622451</v>
+        <v>0.6723429437248474</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>24.95971564904346</v>
+        <v>23.71172986659128</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.06748099557062871</v>
+        <v>0.0673394128200781</v>
       </c>
       <c r="C22">
-        <v>647.0678850238492</v>
+        <v>639.3843949984572</v>
       </c>
       <c r="D22">
-        <v>581.1078850238492</v>
+        <v>581.5613949984572</v>
       </c>
       <c r="E22">
-        <v>-153.16</v>
+        <v>-145.0229999999999</v>
       </c>
       <c r="F22">
-        <v>162.74</v>
+        <v>170.877</v>
       </c>
       <c r="G22">
         <v>228.7</v>
@@ -3085,28 +3085,28 @@
         <v>194.1</v>
       </c>
       <c r="M22">
-        <v>8.185822</v>
+        <v>8.595113100000001</v>
       </c>
       <c r="N22">
-        <v>185.914178</v>
+        <v>185.5048869</v>
       </c>
       <c r="O22">
-        <v>46.3669959932</v>
+        <v>46.26491879286</v>
       </c>
       <c r="P22">
-        <v>139.5471820068</v>
+        <v>139.23996810714</v>
       </c>
       <c r="Q22">
-        <v>200.1471820068</v>
+        <v>199.83996810714</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07491244946328589</v>
+        <v>0.0752035759747824</v>
       </c>
       <c r="T22">
-        <v>0.6723429437248474</v>
+        <v>0.6790664197409331</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>23.71172986659128</v>
+        <v>22.58259987294408</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.0673394128200781</v>
+        <v>0.06719783006952748</v>
       </c>
       <c r="C23">
-        <v>639.3843949984573</v>
+        <v>631.7016133851806</v>
       </c>
       <c r="D23">
-        <v>581.5613949984572</v>
+        <v>582.0156133851807</v>
       </c>
       <c r="E23">
-        <v>-145.023</v>
+        <v>-136.886</v>
       </c>
       <c r="F23">
-        <v>170.877</v>
+        <v>179.014</v>
       </c>
       <c r="G23">
         <v>228.7</v>
@@ -3167,28 +3167,28 @@
         <v>194.1</v>
       </c>
       <c r="M23">
-        <v>8.595113100000001</v>
+        <v>9.0044042</v>
       </c>
       <c r="N23">
-        <v>185.5048869</v>
+        <v>185.0955958</v>
       </c>
       <c r="O23">
-        <v>46.26491879286</v>
+        <v>46.16284159252</v>
       </c>
       <c r="P23">
-        <v>139.23996810714</v>
+        <v>138.93275420748</v>
       </c>
       <c r="Q23">
-        <v>199.83996810714</v>
+        <v>199.53275420748</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.0752035759747824</v>
+        <v>0.07550216726862498</v>
       </c>
       <c r="T23">
-        <v>0.6790664197409331</v>
+        <v>0.6859622925779442</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>22.58259987294408</v>
+        <v>21.55611806053753</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.06719783006952748</v>
+        <v>0.06705624731897689</v>
       </c>
       <c r="C24">
-        <v>631.7016133851806</v>
+        <v>624.0195418451956</v>
       </c>
       <c r="D24">
-        <v>582.0156133851807</v>
+        <v>582.4705418451957</v>
       </c>
       <c r="E24">
-        <v>-136.886</v>
+        <v>-128.749</v>
       </c>
       <c r="F24">
-        <v>179.014</v>
+        <v>187.151</v>
       </c>
       <c r="G24">
         <v>228.7</v>
@@ -3249,28 +3249,28 @@
         <v>194.1</v>
       </c>
       <c r="M24">
-        <v>9.0044042</v>
+        <v>9.413695300000001</v>
       </c>
       <c r="N24">
-        <v>185.0955958</v>
+        <v>184.6863047</v>
       </c>
       <c r="O24">
-        <v>46.16284159252</v>
+        <v>46.06076439218</v>
       </c>
       <c r="P24">
-        <v>138.93275420748</v>
+        <v>138.62554030782</v>
       </c>
       <c r="Q24">
-        <v>199.53275420748</v>
+        <v>199.22554030782</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07550216726862498</v>
+        <v>0.07580851418048945</v>
       </c>
       <c r="T24">
-        <v>0.6859622925779442</v>
+        <v>0.6930372789951373</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>21.55611806053753</v>
+        <v>20.61889553616633</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.06705624731897689</v>
+        <v>0.06691466456842626</v>
       </c>
       <c r="C25">
-        <v>624.0195418451956</v>
+        <v>616.3381820448765</v>
       </c>
       <c r="D25">
-        <v>582.4705418451957</v>
+        <v>582.9261820448764</v>
       </c>
       <c r="E25">
-        <v>-128.749</v>
+        <v>-120.6119999999999</v>
       </c>
       <c r="F25">
-        <v>187.151</v>
+        <v>195.288</v>
       </c>
       <c r="G25">
         <v>228.7</v>
@@ -3331,28 +3331,28 @@
         <v>194.1</v>
       </c>
       <c r="M25">
-        <v>9.413695300000001</v>
+        <v>9.822986400000001</v>
       </c>
       <c r="N25">
-        <v>184.6863047</v>
+        <v>184.2770136</v>
       </c>
       <c r="O25">
-        <v>46.06076439218</v>
+        <v>45.95868719184001</v>
       </c>
       <c r="P25">
-        <v>138.62554030782</v>
+        <v>138.31832640816</v>
       </c>
       <c r="Q25">
-        <v>199.22554030782</v>
+        <v>198.91832640816</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07580851418048945</v>
+        <v>0.07612292285319244</v>
       </c>
       <c r="T25">
-        <v>0.6930372789951373</v>
+        <v>0.7002984492654145</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>20.61889553616633</v>
+        <v>19.75977488882607</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.06691466456842625</v>
+        <v>0.06677308181787564</v>
       </c>
       <c r="C26">
-        <v>616.3381820448765</v>
+        <v>608.6575356558151</v>
       </c>
       <c r="D26">
-        <v>582.9261820448764</v>
+        <v>583.3825356558151</v>
       </c>
       <c r="E26">
-        <v>-120.612</v>
+        <v>-112.475</v>
       </c>
       <c r="F26">
-        <v>195.288</v>
+        <v>203.425</v>
       </c>
       <c r="G26">
         <v>228.7</v>
@@ -3413,28 +3413,28 @@
         <v>194.1</v>
       </c>
       <c r="M26">
-        <v>9.8229864</v>
+        <v>10.2322775</v>
       </c>
       <c r="N26">
-        <v>184.2770136</v>
+        <v>183.8677225</v>
       </c>
       <c r="O26">
-        <v>45.95868719184001</v>
+        <v>45.8566099915</v>
       </c>
       <c r="P26">
-        <v>138.31832640816</v>
+        <v>138.0111125085</v>
       </c>
       <c r="Q26">
-        <v>198.91832640816</v>
+        <v>198.6111125085</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07612292285319244</v>
+        <v>0.07644571575716752</v>
       </c>
       <c r="T26">
-        <v>0.7002984492654145</v>
+        <v>0.7077532507428991</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>19.75977488882607</v>
+        <v>18.96938389327303</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.06677308181787564</v>
+        <v>0.06663149906732503</v>
       </c>
       <c r="C27">
-        <v>608.6575356558151</v>
+        <v>600.9776043548426</v>
       </c>
       <c r="D27">
-        <v>583.3825356558151</v>
+        <v>583.8396043548427</v>
       </c>
       <c r="E27">
-        <v>-112.475</v>
+        <v>-104.338</v>
       </c>
       <c r="F27">
-        <v>203.425</v>
+        <v>211.562</v>
       </c>
       <c r="G27">
         <v>228.7</v>
@@ -3495,28 +3495,28 @@
         <v>194.1</v>
       </c>
       <c r="M27">
-        <v>10.2322775</v>
+        <v>10.6415686</v>
       </c>
       <c r="N27">
-        <v>183.8677225</v>
+        <v>183.4584314</v>
       </c>
       <c r="O27">
-        <v>45.8566099915</v>
+        <v>45.75453279116</v>
       </c>
       <c r="P27">
-        <v>138.0111125085</v>
+        <v>137.70389860884</v>
       </c>
       <c r="Q27">
-        <v>198.6111125085</v>
+        <v>198.30389860884</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07644571575716752</v>
+        <v>0.07677723279368248</v>
       </c>
       <c r="T27">
-        <v>0.7077532507428991</v>
+        <v>0.7154095333413968</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>18.96938389327303</v>
+        <v>18.23979220507022</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.06663149906732503</v>
+        <v>0.06648991631677441</v>
       </c>
       <c r="C28">
-        <v>600.9776043548426</v>
+        <v>593.2983898240491</v>
       </c>
       <c r="D28">
-        <v>583.8396043548427</v>
+        <v>584.2973898240491</v>
       </c>
       <c r="E28">
-        <v>-104.338</v>
+        <v>-96.20099999999994</v>
       </c>
       <c r="F28">
-        <v>211.562</v>
+        <v>219.699</v>
       </c>
       <c r="G28">
         <v>228.7</v>
@@ -3577,28 +3577,28 @@
         <v>194.1</v>
       </c>
       <c r="M28">
-        <v>10.6415686</v>
+        <v>11.0508597</v>
       </c>
       <c r="N28">
-        <v>183.4584314</v>
+        <v>183.0491403</v>
       </c>
       <c r="O28">
-        <v>45.75453279116</v>
+        <v>45.65245559082</v>
       </c>
       <c r="P28">
-        <v>137.70389860884</v>
+        <v>137.39668470918</v>
       </c>
       <c r="Q28">
-        <v>198.30389860884</v>
+        <v>197.99668470918</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07677723279368248</v>
+        <v>0.07711783248873208</v>
       </c>
       <c r="T28">
-        <v>0.7154095333413968</v>
+        <v>0.7232755771069765</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>18.23979220507022</v>
+        <v>17.56424434562317</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.06648991631677441</v>
+        <v>0.0663483335662238</v>
       </c>
       <c r="C29">
-        <v>593.2983898240491</v>
+        <v>585.6198937508043</v>
       </c>
       <c r="D29">
-        <v>584.2973898240491</v>
+        <v>584.7558937508044</v>
       </c>
       <c r="E29">
-        <v>-96.20099999999994</v>
+        <v>-88.06399999999994</v>
       </c>
       <c r="F29">
-        <v>219.699</v>
+        <v>227.836</v>
       </c>
       <c r="G29">
         <v>228.7</v>
@@ -3659,28 +3659,28 @@
         <v>194.1</v>
       </c>
       <c r="M29">
-        <v>11.0508597</v>
+        <v>11.4601508</v>
       </c>
       <c r="N29">
-        <v>183.0491403</v>
+        <v>182.6398492</v>
       </c>
       <c r="O29">
-        <v>45.65245559082</v>
+        <v>45.55037839048</v>
       </c>
       <c r="P29">
-        <v>137.39668470918</v>
+        <v>137.08947080952</v>
       </c>
       <c r="Q29">
-        <v>197.99668470918</v>
+        <v>197.68947080952</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07711783248873208</v>
+        <v>0.07746789328642195</v>
       </c>
       <c r="T29">
-        <v>0.7232755771069765</v>
+        <v>0.731360122088267</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>17.56424434562317</v>
+        <v>16.93694990470806</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.0663483335662238</v>
+        <v>0.06620675081567319</v>
       </c>
       <c r="C30">
-        <v>585.6198937508043</v>
+        <v>577.942117827779</v>
       </c>
       <c r="D30">
-        <v>584.7558937508044</v>
+        <v>585.2151178277791</v>
       </c>
       <c r="E30">
-        <v>-88.06399999999994</v>
+        <v>-79.92699999999994</v>
       </c>
       <c r="F30">
-        <v>227.836</v>
+        <v>235.973</v>
       </c>
       <c r="G30">
         <v>228.7</v>
@@ -3741,28 +3741,28 @@
         <v>194.1</v>
       </c>
       <c r="M30">
-        <v>11.4601508</v>
+        <v>11.8694419</v>
       </c>
       <c r="N30">
-        <v>182.6398492</v>
+        <v>182.2305581</v>
       </c>
       <c r="O30">
-        <v>45.55037839048</v>
+        <v>45.44830119014</v>
       </c>
       <c r="P30">
-        <v>137.08947080952</v>
+        <v>136.78225690986</v>
       </c>
       <c r="Q30">
-        <v>197.68947080952</v>
+        <v>197.38225690986</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.07746789328642195</v>
+        <v>0.07782781495165239</v>
       </c>
       <c r="T30">
-        <v>0.731360122088267</v>
+        <v>0.7396724007310022</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>16.93694990470806</v>
+        <v>16.3529171493733</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.06620675081567319</v>
+        <v>0.06606516806512257</v>
       </c>
       <c r="C31">
-        <v>577.9421178277792</v>
+        <v>570.2650637529647</v>
       </c>
       <c r="D31">
-        <v>585.2151178277791</v>
+        <v>585.6750637529648</v>
       </c>
       <c r="E31">
-        <v>-79.92699999999999</v>
+        <v>-71.78999999999996</v>
       </c>
       <c r="F31">
-        <v>235.973</v>
+        <v>244.11</v>
       </c>
       <c r="G31">
         <v>228.7</v>
@@ -3823,28 +3823,28 @@
         <v>194.1</v>
       </c>
       <c r="M31">
-        <v>11.8694419</v>
+        <v>12.278733</v>
       </c>
       <c r="N31">
-        <v>182.2305581</v>
+        <v>181.821267</v>
       </c>
       <c r="O31">
-        <v>45.44830119014</v>
+        <v>45.3462239898</v>
       </c>
       <c r="P31">
-        <v>136.78225690986</v>
+        <v>136.4750430102</v>
       </c>
       <c r="Q31">
-        <v>197.38225690986</v>
+        <v>197.0750430102</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.07782781495165239</v>
+        <v>0.07819802009303226</v>
       </c>
       <c r="T31">
-        <v>0.739672400731002</v>
+        <v>0.748222173049244</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>16.3529171493733</v>
+        <v>15.80781991106086</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.06606516806512257</v>
+        <v>0.06592358531457197</v>
       </c>
       <c r="C32">
-        <v>570.2650637529647</v>
+        <v>562.5887332296954</v>
       </c>
       <c r="D32">
-        <v>585.6750637529648</v>
+        <v>586.1357332296956</v>
       </c>
       <c r="E32">
-        <v>-71.78999999999996</v>
+        <v>-63.65299999999996</v>
       </c>
       <c r="F32">
-        <v>244.11</v>
+        <v>252.247</v>
       </c>
       <c r="G32">
         <v>228.7</v>
@@ -3905,28 +3905,28 @@
         <v>194.1</v>
       </c>
       <c r="M32">
-        <v>12.278733</v>
+        <v>12.6880241</v>
       </c>
       <c r="N32">
-        <v>181.821267</v>
+        <v>181.4119759</v>
       </c>
       <c r="O32">
-        <v>45.3462239898</v>
+        <v>45.24414678946</v>
       </c>
       <c r="P32">
-        <v>136.4750430102</v>
+        <v>136.16782911054</v>
       </c>
       <c r="Q32">
-        <v>197.0750430102</v>
+        <v>196.76782911054</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.07819802009303226</v>
+        <v>0.07857895581822025</v>
       </c>
       <c r="T32">
-        <v>0.748222173049244</v>
+        <v>0.7570197648549711</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>15.80781991106086</v>
+        <v>15.29789023651051</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.06592358531457197</v>
+        <v>0.06578200256402135</v>
       </c>
       <c r="C33">
-        <v>562.5887332296954</v>
+        <v>554.913127966669</v>
       </c>
       <c r="D33">
-        <v>586.1357332296956</v>
+        <v>586.5971279666691</v>
       </c>
       <c r="E33">
-        <v>-63.65299999999996</v>
+        <v>-55.51599999999996</v>
       </c>
       <c r="F33">
-        <v>252.247</v>
+        <v>260.384</v>
       </c>
       <c r="G33">
         <v>228.7</v>
@@ -3987,28 +3987,28 @@
         <v>194.1</v>
       </c>
       <c r="M33">
-        <v>12.6880241</v>
+        <v>13.0973152</v>
       </c>
       <c r="N33">
-        <v>181.4119759</v>
+        <v>181.0026848</v>
       </c>
       <c r="O33">
-        <v>45.24414678946</v>
+        <v>45.14206958912</v>
       </c>
       <c r="P33">
-        <v>136.16782911054</v>
+        <v>135.86061521088</v>
       </c>
       <c r="Q33">
-        <v>196.76782911054</v>
+        <v>196.46061521088</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.07857895581822025</v>
+        <v>0.07897109553532553</v>
       </c>
       <c r="T33">
-        <v>0.7570197648549711</v>
+        <v>0.7660761093608667</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>15.29789023651051</v>
+        <v>14.81983116661955</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.06578200256402135</v>
+        <v>0.06564041981347074</v>
       </c>
       <c r="C34">
-        <v>554.913127966669</v>
+        <v>547.2382496779671</v>
       </c>
       <c r="D34">
-        <v>586.5971279666691</v>
+        <v>587.059249677967</v>
       </c>
       <c r="E34">
-        <v>-55.51599999999996</v>
+        <v>-47.37899999999996</v>
       </c>
       <c r="F34">
-        <v>260.384</v>
+        <v>268.521</v>
       </c>
       <c r="G34">
         <v>228.7</v>
@@ -4069,28 +4069,28 @@
         <v>194.1</v>
       </c>
       <c r="M34">
-        <v>13.0973152</v>
+        <v>13.5066063</v>
       </c>
       <c r="N34">
-        <v>181.0026848</v>
+        <v>180.5933937</v>
       </c>
       <c r="O34">
-        <v>45.14206958912</v>
+        <v>45.03999238878001</v>
       </c>
       <c r="P34">
-        <v>135.86061521088</v>
+        <v>135.55340131122</v>
       </c>
       <c r="Q34">
-        <v>196.46061521088</v>
+        <v>196.15340131122</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.07897109553532553</v>
+        <v>0.07937494091562798</v>
       </c>
       <c r="T34">
-        <v>0.7660761093608667</v>
+        <v>0.7754027925087293</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>14.81983116661955</v>
+        <v>14.37074537369169</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.06564041981347074</v>
+        <v>0.06549883706292012</v>
       </c>
       <c r="C35">
-        <v>547.2382496779671</v>
+        <v>539.5641000830771</v>
       </c>
       <c r="D35">
-        <v>587.059249677967</v>
+        <v>587.5221000830771</v>
       </c>
       <c r="E35">
-        <v>-47.37899999999996</v>
+        <v>-39.24199999999996</v>
       </c>
       <c r="F35">
-        <v>268.521</v>
+        <v>276.658</v>
       </c>
       <c r="G35">
         <v>228.7</v>
@@ -4151,28 +4151,28 @@
         <v>194.1</v>
       </c>
       <c r="M35">
-        <v>13.5066063</v>
+        <v>13.9158974</v>
       </c>
       <c r="N35">
-        <v>180.5933937</v>
+        <v>180.1841026</v>
       </c>
       <c r="O35">
-        <v>45.03999238878001</v>
+        <v>44.93791518844</v>
       </c>
       <c r="P35">
-        <v>135.55340131122</v>
+        <v>135.24618741156</v>
       </c>
       <c r="Q35">
-        <v>196.15340131122</v>
+        <v>195.84618741156</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.07937494091562798</v>
+        <v>0.07979102403472747</v>
       </c>
       <c r="T35">
-        <v>0.7754027925087293</v>
+        <v>0.7850121024186484</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>14.37074537369169</v>
+        <v>13.94807639211252</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.06549883706292012</v>
+        <v>0.06535725431236951</v>
       </c>
       <c r="C36">
-        <v>539.5641000830771</v>
+        <v>531.8906809069138</v>
       </c>
       <c r="D36">
-        <v>587.5221000830771</v>
+        <v>587.9856809069139</v>
       </c>
       <c r="E36">
-        <v>-39.24199999999996</v>
+        <v>-31.10499999999996</v>
       </c>
       <c r="F36">
-        <v>276.658</v>
+        <v>284.795</v>
       </c>
       <c r="G36">
         <v>228.7</v>
@@ -4233,28 +4233,28 @@
         <v>194.1</v>
       </c>
       <c r="M36">
-        <v>13.9158974</v>
+        <v>14.3251885</v>
       </c>
       <c r="N36">
-        <v>180.1841026</v>
+        <v>179.7748115</v>
       </c>
       <c r="O36">
-        <v>44.93791518844</v>
+        <v>44.8358379881</v>
       </c>
       <c r="P36">
-        <v>135.24618741156</v>
+        <v>134.9389735119</v>
       </c>
       <c r="Q36">
-        <v>195.84618741156</v>
+        <v>195.5389735119</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.07979102403472747</v>
+        <v>0.08021990971133772</v>
       </c>
       <c r="T36">
-        <v>0.7850121024186484</v>
+        <v>0.7949170834027188</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>13.94807639211252</v>
+        <v>13.54955992376645</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.06535725431236951</v>
+        <v>0.0652156715618189</v>
       </c>
       <c r="C37">
-        <v>531.8906809069138</v>
+        <v>524.2179938798404</v>
       </c>
       <c r="D37">
-        <v>587.9856809069139</v>
+        <v>588.4499938798403</v>
       </c>
       <c r="E37">
-        <v>-31.10499999999996</v>
+        <v>-22.9679999999999</v>
       </c>
       <c r="F37">
-        <v>284.795</v>
+        <v>292.9320000000001</v>
       </c>
       <c r="G37">
         <v>228.7</v>
@@ -4315,28 +4315,28 @@
         <v>194.1</v>
       </c>
       <c r="M37">
-        <v>14.3251885</v>
+        <v>14.7344796</v>
       </c>
       <c r="N37">
-        <v>179.7748115</v>
+        <v>179.3655204</v>
       </c>
       <c r="O37">
-        <v>44.8358379881</v>
+        <v>44.73376078776</v>
       </c>
       <c r="P37">
-        <v>134.9389735119</v>
+        <v>134.63175961224</v>
       </c>
       <c r="Q37">
-        <v>195.5389735119</v>
+        <v>195.23175961224</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08021990971133772</v>
+        <v>0.08066219806534206</v>
       </c>
       <c r="T37">
-        <v>0.7949170834027188</v>
+        <v>0.8051315950425415</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>13.54955992376645</v>
+        <v>13.17318325921738</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.06521567156181891</v>
+        <v>0.0654906718112683</v>
       </c>
       <c r="C38">
-        <v>524.2179938798404</v>
+        <v>515.1798154963622</v>
       </c>
       <c r="D38">
-        <v>588.4499938798403</v>
+        <v>587.5488154963622</v>
       </c>
       <c r="E38">
-        <v>-22.96799999999996</v>
+        <v>-14.83099999999996</v>
       </c>
       <c r="F38">
-        <v>292.932</v>
+        <v>301.069</v>
       </c>
       <c r="G38">
         <v>228.7</v>
@@ -4397,45 +4397,45 @@
         <v>194.1</v>
       </c>
       <c r="M38">
-        <v>14.7344796</v>
+        <v>15.5953742</v>
       </c>
       <c r="N38">
-        <v>179.3655204</v>
+        <v>178.5046258</v>
       </c>
       <c r="O38">
-        <v>44.73376078776</v>
+        <v>44.51905367451999</v>
       </c>
       <c r="P38">
-        <v>134.63175961224</v>
+        <v>133.98557212548</v>
       </c>
       <c r="Q38">
-        <v>195.23175961224</v>
+        <v>194.58557212548</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08066219806534206</v>
+        <v>0.08111852731947349</v>
       </c>
       <c r="T38">
-        <v>0.8051315950425415</v>
+        <v>0.815670376893152</v>
       </c>
       <c r="U38">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V38">
         <v>0.2494</v>
       </c>
       <c r="W38">
-        <v>0.03775517999999999</v>
+        <v>0.03888108</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y38">
-        <v>13.17318325921738</v>
+        <v>12.44599824991695</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.0654906718112683</v>
+        <v>0.06536034806071768</v>
       </c>
       <c r="C39">
-        <v>515.1798154963622</v>
+        <v>507.4695433067869</v>
       </c>
       <c r="D39">
-        <v>587.5488154963622</v>
+        <v>587.975543306787</v>
       </c>
       <c r="E39">
-        <v>-14.83099999999996</v>
+        <v>-6.69399999999996</v>
       </c>
       <c r="F39">
-        <v>301.069</v>
+        <v>309.206</v>
       </c>
       <c r="G39">
         <v>228.7</v>
@@ -4479,28 +4479,28 @@
         <v>194.1</v>
       </c>
       <c r="M39">
-        <v>15.5953742</v>
+        <v>16.0168708</v>
       </c>
       <c r="N39">
-        <v>178.5046258</v>
+        <v>178.0831292</v>
       </c>
       <c r="O39">
-        <v>44.51905367451999</v>
+        <v>44.41393242248</v>
       </c>
       <c r="P39">
-        <v>133.98557212548</v>
+        <v>133.66919677752</v>
       </c>
       <c r="Q39">
-        <v>194.58557212548</v>
+        <v>194.26919677752</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08111852731947349</v>
+        <v>0.08158957687212529</v>
       </c>
       <c r="T39">
-        <v>0.815670376893152</v>
+        <v>0.8265491194486211</v>
       </c>
       <c r="U39">
         <v>0.0518</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>12.44599824991695</v>
+        <v>12.1184719801823</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.06536034806071768</v>
+        <v>0.06523002431016707</v>
       </c>
       <c r="C40">
-        <v>507.4695433067869</v>
+        <v>499.7598914196261</v>
       </c>
       <c r="D40">
-        <v>587.975543306787</v>
+        <v>588.402891419626</v>
       </c>
       <c r="E40">
-        <v>-6.69399999999996</v>
+        <v>1.44300000000004</v>
       </c>
       <c r="F40">
-        <v>309.206</v>
+        <v>317.343</v>
       </c>
       <c r="G40">
         <v>228.7</v>
@@ -4561,28 +4561,28 @@
         <v>194.1</v>
       </c>
       <c r="M40">
-        <v>16.0168708</v>
+        <v>16.4383674</v>
       </c>
       <c r="N40">
-        <v>178.0831292</v>
+        <v>177.6616326</v>
       </c>
       <c r="O40">
-        <v>44.41393242248</v>
+        <v>44.30881117044</v>
       </c>
       <c r="P40">
-        <v>133.66919677752</v>
+        <v>133.35282142956</v>
       </c>
       <c r="Q40">
-        <v>194.26919677752</v>
+        <v>193.95282142956</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08158957687212529</v>
+        <v>0.08207607067240504</v>
       </c>
       <c r="T40">
-        <v>0.8265491194486211</v>
+        <v>0.8377845420878761</v>
       </c>
       <c r="U40">
         <v>0.0518</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>12.1184719801823</v>
+        <v>11.80774192940839</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.06523002431016707</v>
+        <v>0.06509970055961646</v>
       </c>
       <c r="C41">
-        <v>499.7598914196261</v>
+        <v>492.050861188394</v>
       </c>
       <c r="D41">
-        <v>588.402891419626</v>
+        <v>588.830861188394</v>
       </c>
       <c r="E41">
-        <v>1.44300000000004</v>
+        <v>9.580000000000041</v>
       </c>
       <c r="F41">
-        <v>317.343</v>
+        <v>325.48</v>
       </c>
       <c r="G41">
         <v>228.7</v>
@@ -4643,28 +4643,28 @@
         <v>194.1</v>
       </c>
       <c r="M41">
-        <v>16.4383674</v>
+        <v>16.859864</v>
       </c>
       <c r="N41">
-        <v>177.6616326</v>
+        <v>177.240136</v>
       </c>
       <c r="O41">
-        <v>44.30881117044</v>
+        <v>44.2036899184</v>
       </c>
       <c r="P41">
-        <v>133.35282142956</v>
+        <v>133.0364460816</v>
       </c>
       <c r="Q41">
-        <v>193.95282142956</v>
+        <v>193.6364460816</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08207607067240504</v>
+        <v>0.08257878093269411</v>
       </c>
       <c r="T41">
-        <v>0.8377845420878761</v>
+        <v>0.8493944788151062</v>
       </c>
       <c r="U41">
         <v>0.0518</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>11.80774192940839</v>
+        <v>11.51254838117318</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.06509970055961646</v>
+        <v>0.06496937680906584</v>
       </c>
       <c r="C42">
-        <v>492.050861188394</v>
+        <v>484.3424539705465</v>
       </c>
       <c r="D42">
-        <v>588.830861188394</v>
+        <v>589.2594539705466</v>
       </c>
       <c r="E42">
-        <v>9.580000000000041</v>
+        <v>17.71700000000004</v>
       </c>
       <c r="F42">
-        <v>325.48</v>
+        <v>333.617</v>
       </c>
       <c r="G42">
         <v>228.7</v>
@@ -4725,28 +4725,28 @@
         <v>194.1</v>
       </c>
       <c r="M42">
-        <v>16.859864</v>
+        <v>17.2813606</v>
       </c>
       <c r="N42">
-        <v>177.240136</v>
+        <v>176.8186394</v>
       </c>
       <c r="O42">
-        <v>44.2036899184</v>
+        <v>44.09856866636</v>
       </c>
       <c r="P42">
-        <v>133.0364460816</v>
+        <v>132.72007073364</v>
       </c>
       <c r="Q42">
-        <v>193.6364460816</v>
+        <v>193.32007073364</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08257878093269411</v>
+        <v>0.08309853221875567</v>
       </c>
       <c r="T42">
-        <v>0.8493944788151062</v>
+        <v>0.8613979727195306</v>
       </c>
       <c r="U42">
         <v>0.0518</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>11.51254838117318</v>
+        <v>11.23175451821774</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.06496937680906584</v>
+        <v>0.06483905305851523</v>
       </c>
       <c r="C43">
-        <v>484.3424539705465</v>
+        <v>476.6346711274942</v>
       </c>
       <c r="D43">
-        <v>589.2594539705466</v>
+        <v>589.6886711274942</v>
       </c>
       <c r="E43">
-        <v>17.71700000000004</v>
+        <v>25.8540000000001</v>
       </c>
       <c r="F43">
-        <v>333.617</v>
+        <v>341.7540000000001</v>
       </c>
       <c r="G43">
         <v>228.7</v>
@@ -4807,28 +4807,28 @@
         <v>194.1</v>
       </c>
       <c r="M43">
-        <v>17.2813606</v>
+        <v>17.7028572</v>
       </c>
       <c r="N43">
-        <v>176.8186394</v>
+        <v>176.3971428</v>
       </c>
       <c r="O43">
-        <v>44.09856866636</v>
+        <v>43.99344741431999</v>
       </c>
       <c r="P43">
-        <v>132.72007073364</v>
+        <v>132.40369538568</v>
       </c>
       <c r="Q43">
-        <v>193.32007073364</v>
+        <v>193.00369538568</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08309853221875567</v>
+        <v>0.08363620596295729</v>
       </c>
       <c r="T43">
-        <v>0.8613979727195306</v>
+        <v>0.873815380206866</v>
       </c>
       <c r="U43">
         <v>0.0518</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>11.23175451821774</v>
+        <v>10.9643317915935</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.06483905305851523</v>
+        <v>0.06470872930796462</v>
       </c>
       <c r="C44">
-        <v>476.6346711274942</v>
+        <v>468.9275140246173</v>
       </c>
       <c r="D44">
-        <v>589.6886711274942</v>
+        <v>590.1185140246173</v>
       </c>
       <c r="E44">
-        <v>25.85400000000004</v>
+        <v>33.99100000000004</v>
       </c>
       <c r="F44">
-        <v>341.754</v>
+        <v>349.891</v>
       </c>
       <c r="G44">
         <v>228.7</v>
@@ -4889,28 +4889,28 @@
         <v>194.1</v>
       </c>
       <c r="M44">
-        <v>17.7028572</v>
+        <v>18.1243538</v>
       </c>
       <c r="N44">
-        <v>176.3971428</v>
+        <v>175.9756462</v>
       </c>
       <c r="O44">
-        <v>43.99344741431999</v>
+        <v>43.88832616228</v>
       </c>
       <c r="P44">
-        <v>132.40369538568</v>
+        <v>132.08732003772</v>
       </c>
       <c r="Q44">
-        <v>193.00369538568</v>
+        <v>192.68732003772</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08363620596295729</v>
+        <v>0.08419274545256951</v>
       </c>
       <c r="T44">
-        <v>0.8738153802068659</v>
+        <v>0.886668486202529</v>
       </c>
       <c r="U44">
         <v>0.0518</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>10.96433179159351</v>
+        <v>10.70934733132389</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.06470872930796462</v>
+        <v>0.06457840555741401</v>
       </c>
       <c r="C45">
-        <v>468.9275140246173</v>
+        <v>461.2209840312798</v>
       </c>
       <c r="D45">
-        <v>590.1185140246173</v>
+        <v>590.5489840312798</v>
       </c>
       <c r="E45">
-        <v>33.99100000000004</v>
+        <v>42.12800000000004</v>
       </c>
       <c r="F45">
-        <v>349.891</v>
+        <v>358.028</v>
       </c>
       <c r="G45">
         <v>228.7</v>
@@ -4971,28 +4971,28 @@
         <v>194.1</v>
       </c>
       <c r="M45">
-        <v>18.1243538</v>
+        <v>18.5458504</v>
       </c>
       <c r="N45">
-        <v>175.9756462</v>
+        <v>175.5541496</v>
       </c>
       <c r="O45">
-        <v>43.88832616228</v>
+        <v>43.78320491024</v>
       </c>
       <c r="P45">
-        <v>132.08732003772</v>
+        <v>131.77094468976</v>
       </c>
       <c r="Q45">
-        <v>192.68732003772</v>
+        <v>192.37094468976</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08419274545256951</v>
+        <v>0.08476916135252502</v>
       </c>
       <c r="T45">
-        <v>0.886668486202529</v>
+        <v>0.8999806316980372</v>
       </c>
       <c r="U45">
         <v>0.0518</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>10.70934733132389</v>
+        <v>10.4659530737938</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.06457840555741401</v>
+        <v>0.0644480818068634</v>
       </c>
       <c r="C46">
-        <v>461.2209840312798</v>
+        <v>453.5150825208445</v>
       </c>
       <c r="D46">
-        <v>590.5489840312798</v>
+        <v>590.9800825208446</v>
       </c>
       <c r="E46">
-        <v>42.12800000000004</v>
+        <v>50.26500000000004</v>
       </c>
       <c r="F46">
-        <v>358.028</v>
+        <v>366.165</v>
       </c>
       <c r="G46">
         <v>228.7</v>
@@ -5053,28 +5053,28 @@
         <v>194.1</v>
       </c>
       <c r="M46">
-        <v>18.5458504</v>
+        <v>18.967347</v>
       </c>
       <c r="N46">
-        <v>175.5541496</v>
+        <v>175.132653</v>
       </c>
       <c r="O46">
-        <v>43.78320491024</v>
+        <v>43.6780836582</v>
       </c>
       <c r="P46">
-        <v>131.77094468976</v>
+        <v>131.4545693418</v>
       </c>
       <c r="Q46">
-        <v>192.37094468976</v>
+        <v>192.0545693418</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08476916135252502</v>
+        <v>0.08536653783066073</v>
       </c>
       <c r="T46">
-        <v>0.8999806316980372</v>
+        <v>0.9137768552115639</v>
       </c>
       <c r="U46">
         <v>0.0518</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>10.4659530737938</v>
+        <v>10.23337633882061</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.0644480818068634</v>
+        <v>0.06431775805631279</v>
       </c>
       <c r="C47">
-        <v>453.5150825208445</v>
+        <v>445.8098108706871</v>
       </c>
       <c r="D47">
-        <v>590.9800825208446</v>
+        <v>591.4118108706872</v>
       </c>
       <c r="E47">
-        <v>50.26500000000004</v>
+        <v>58.40200000000004</v>
       </c>
       <c r="F47">
-        <v>366.165</v>
+        <v>374.302</v>
       </c>
       <c r="G47">
         <v>228.7</v>
@@ -5135,28 +5135,28 @@
         <v>194.1</v>
       </c>
       <c r="M47">
-        <v>18.967347</v>
+        <v>19.3888436</v>
       </c>
       <c r="N47">
-        <v>175.132653</v>
+        <v>174.7111564</v>
       </c>
       <c r="O47">
-        <v>43.6780836582</v>
+        <v>43.57296240616</v>
       </c>
       <c r="P47">
-        <v>131.4545693418</v>
+        <v>131.13819399384</v>
       </c>
       <c r="Q47">
-        <v>192.0545693418</v>
+        <v>191.73819399384</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08536653783066073</v>
+        <v>0.08598603936354218</v>
       </c>
       <c r="T47">
-        <v>0.9137768552115639</v>
+        <v>0.9280840499663323</v>
       </c>
       <c r="U47">
         <v>0.0518</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>10.23337633882061</v>
+        <v>10.01091163580277</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.06431775805631279</v>
+        <v>0.06478716370576218</v>
       </c>
       <c r="C48">
-        <v>445.8098108706871</v>
+        <v>436.1207411663639</v>
       </c>
       <c r="D48">
-        <v>591.4118108706872</v>
+        <v>589.8597411663638</v>
       </c>
       <c r="E48">
-        <v>58.40200000000004</v>
+        <v>66.53900000000004</v>
       </c>
       <c r="F48">
-        <v>374.302</v>
+        <v>382.439</v>
       </c>
       <c r="G48">
         <v>228.7</v>
@@ -5217,45 +5217,45 @@
         <v>194.1</v>
       </c>
       <c r="M48">
-        <v>19.3888436</v>
+        <v>20.4604865</v>
       </c>
       <c r="N48">
-        <v>174.7111564</v>
+        <v>173.6395135</v>
       </c>
       <c r="O48">
-        <v>43.57296240616</v>
+        <v>43.3056946669</v>
       </c>
       <c r="P48">
-        <v>131.13819399384</v>
+        <v>130.3338188331</v>
       </c>
       <c r="Q48">
-        <v>191.73819399384</v>
+        <v>190.9338188331</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.08598603936354218</v>
+        <v>0.08662891831275882</v>
       </c>
       <c r="T48">
-        <v>0.9280840499663323</v>
+        <v>0.9429311388627901</v>
       </c>
       <c r="U48">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V48">
         <v>0.2494</v>
       </c>
       <c r="W48">
-        <v>0.03888108</v>
+        <v>0.04015709999999999</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y48">
-        <v>10.01091163580277</v>
+        <v>9.486577946228207</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.06478716370576218</v>
+        <v>0.06466960015521155</v>
       </c>
       <c r="C49">
-        <v>436.1207411663639</v>
+        <v>428.3716948766009</v>
       </c>
       <c r="D49">
-        <v>589.8597411663638</v>
+        <v>590.247694876601</v>
       </c>
       <c r="E49">
-        <v>66.53900000000004</v>
+        <v>74.6760000000001</v>
       </c>
       <c r="F49">
-        <v>382.439</v>
+        <v>390.5760000000001</v>
       </c>
       <c r="G49">
         <v>228.7</v>
@@ -5299,28 +5299,28 @@
         <v>194.1</v>
       </c>
       <c r="M49">
-        <v>20.4604865</v>
+        <v>20.895816</v>
       </c>
       <c r="N49">
-        <v>173.6395135</v>
+        <v>173.204184</v>
       </c>
       <c r="O49">
-        <v>43.3056946669</v>
+        <v>43.1971234896</v>
       </c>
       <c r="P49">
-        <v>130.3338188331</v>
+        <v>130.0070605104</v>
       </c>
       <c r="Q49">
-        <v>190.9338188331</v>
+        <v>190.6070605104</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.08662891831275882</v>
+        <v>0.08729652337540683</v>
       </c>
       <c r="T49">
-        <v>0.9429311388627901</v>
+        <v>0.9583492696398809</v>
       </c>
       <c r="U49">
         <v>0.0535</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>9.486577946228207</v>
+        <v>9.288940905681788</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.06466960015521155</v>
+        <v>0.06455203660466094</v>
       </c>
       <c r="C50">
-        <v>428.3716948766009</v>
+        <v>420.6231592409001</v>
       </c>
       <c r="D50">
-        <v>590.247694876601</v>
+        <v>590.6361592409</v>
       </c>
       <c r="E50">
-        <v>74.67600000000004</v>
+        <v>82.81300000000005</v>
       </c>
       <c r="F50">
-        <v>390.576</v>
+        <v>398.713</v>
       </c>
       <c r="G50">
         <v>228.7</v>
@@ -5381,28 +5381,28 @@
         <v>194.1</v>
       </c>
       <c r="M50">
-        <v>20.895816</v>
+        <v>21.3311455</v>
       </c>
       <c r="N50">
-        <v>173.204184</v>
+        <v>172.7688545</v>
       </c>
       <c r="O50">
-        <v>43.1971234896</v>
+        <v>43.0885523123</v>
       </c>
       <c r="P50">
-        <v>130.0070605104</v>
+        <v>129.6803021877</v>
       </c>
       <c r="Q50">
-        <v>190.6070605104</v>
+        <v>190.2803021877</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.08729652337540683</v>
+        <v>0.08799030902874695</v>
       </c>
       <c r="T50">
-        <v>0.9583492696398808</v>
+        <v>0.9743720329964654</v>
       </c>
       <c r="U50">
         <v>0.0535</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>9.288940905681788</v>
+        <v>9.099370683116852</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.06455203660466094</v>
+        <v>0.06443447305411033</v>
       </c>
       <c r="C51">
-        <v>420.6231592409001</v>
+        <v>412.8751352681669</v>
       </c>
       <c r="D51">
-        <v>590.6361592409</v>
+        <v>591.025135268167</v>
       </c>
       <c r="E51">
-        <v>82.81300000000005</v>
+        <v>90.95000000000005</v>
       </c>
       <c r="F51">
-        <v>398.713</v>
+        <v>406.85</v>
       </c>
       <c r="G51">
         <v>228.7</v>
@@ -5463,28 +5463,28 @@
         <v>194.1</v>
       </c>
       <c r="M51">
-        <v>21.3311455</v>
+        <v>21.766475</v>
       </c>
       <c r="N51">
-        <v>172.7688545</v>
+        <v>172.333525</v>
       </c>
       <c r="O51">
-        <v>43.0885523123</v>
+        <v>42.979981135</v>
       </c>
       <c r="P51">
-        <v>129.6803021877</v>
+        <v>129.353543865</v>
       </c>
       <c r="Q51">
-        <v>190.2803021877</v>
+        <v>189.953543865</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.08799030902874695</v>
+        <v>0.08871184610822067</v>
       </c>
       <c r="T51">
-        <v>0.9743720329964654</v>
+        <v>0.9910357068873132</v>
       </c>
       <c r="U51">
         <v>0.0535</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>9.099370683116852</v>
+        <v>8.917383269454518</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.06443447305411033</v>
+        <v>0.06431690950355973</v>
       </c>
       <c r="C52">
-        <v>412.8751352681669</v>
+        <v>405.1276239699678</v>
       </c>
       <c r="D52">
-        <v>591.025135268167</v>
+        <v>591.4146239699679</v>
       </c>
       <c r="E52">
-        <v>90.95000000000005</v>
+        <v>99.08700000000005</v>
       </c>
       <c r="F52">
-        <v>406.85</v>
+        <v>414.987</v>
       </c>
       <c r="G52">
         <v>228.7</v>
@@ -5545,28 +5545,28 @@
         <v>194.1</v>
       </c>
       <c r="M52">
-        <v>21.766475</v>
+        <v>22.2018045</v>
       </c>
       <c r="N52">
-        <v>172.333525</v>
+        <v>171.8981955</v>
       </c>
       <c r="O52">
-        <v>42.979981135</v>
+        <v>42.8714099577</v>
       </c>
       <c r="P52">
-        <v>129.353543865</v>
+        <v>129.0267855423</v>
       </c>
       <c r="Q52">
-        <v>189.953543865</v>
+        <v>189.6267855423</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.08871184610822067</v>
+        <v>0.08946283368073413</v>
       </c>
       <c r="T52">
-        <v>0.9910357068873132</v>
+        <v>1.00837953073289</v>
       </c>
       <c r="U52">
         <v>0.0535</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>8.917383269454518</v>
+        <v>8.742532617112271</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.06431690950355973</v>
+        <v>0.06419934595300911</v>
       </c>
       <c r="C53">
-        <v>405.1276239699678</v>
+        <v>397.380626360537</v>
       </c>
       <c r="D53">
-        <v>591.4146239699679</v>
+        <v>591.804626360537</v>
       </c>
       <c r="E53">
-        <v>99.08700000000005</v>
+        <v>107.224</v>
       </c>
       <c r="F53">
-        <v>414.987</v>
+        <v>423.124</v>
       </c>
       <c r="G53">
         <v>228.7</v>
@@ -5627,28 +5627,28 @@
         <v>194.1</v>
       </c>
       <c r="M53">
-        <v>22.2018045</v>
+        <v>22.637134</v>
       </c>
       <c r="N53">
-        <v>171.8981955</v>
+        <v>171.462866</v>
       </c>
       <c r="O53">
-        <v>42.8714099577</v>
+        <v>42.7628387804</v>
       </c>
       <c r="P53">
-        <v>129.0267855423</v>
+        <v>128.7000272196</v>
       </c>
       <c r="Q53">
-        <v>189.6267855423</v>
+        <v>189.3000272196</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.08946283368073413</v>
+        <v>0.09024511240210231</v>
       </c>
       <c r="T53">
-        <v>1.00837953073289</v>
+        <v>1.026446013905365</v>
       </c>
       <c r="U53">
         <v>0.0535</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>8.742532617112271</v>
+        <v>8.574406989860112</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.06419934595300911</v>
+        <v>0.06408178240245849</v>
       </c>
       <c r="C54">
-        <v>397.380626360537</v>
+        <v>389.6341434567852</v>
       </c>
       <c r="D54">
-        <v>591.804626360537</v>
+        <v>592.1951434567853</v>
       </c>
       <c r="E54">
-        <v>107.224</v>
+        <v>115.361</v>
       </c>
       <c r="F54">
-        <v>423.124</v>
+        <v>431.261</v>
       </c>
       <c r="G54">
         <v>228.7</v>
@@ -5709,28 +5709,28 @@
         <v>194.1</v>
       </c>
       <c r="M54">
-        <v>22.637134</v>
+        <v>23.0724635</v>
       </c>
       <c r="N54">
-        <v>171.462866</v>
+        <v>171.0275365</v>
       </c>
       <c r="O54">
-        <v>42.7628387804</v>
+        <v>42.6542676031</v>
       </c>
       <c r="P54">
-        <v>128.7000272196</v>
+        <v>128.3732688969</v>
       </c>
       <c r="Q54">
-        <v>189.3000272196</v>
+        <v>188.9732688969</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09024511240210231</v>
+        <v>0.09106067957969893</v>
       </c>
       <c r="T54">
-        <v>1.026446013905365</v>
+        <v>1.045281283595818</v>
       </c>
       <c r="U54">
         <v>0.0535</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>8.574406989860112</v>
+        <v>8.412625725900487</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.06408178240245849</v>
+        <v>0.06396421885190788</v>
       </c>
       <c r="C55">
-        <v>389.6341434567852</v>
+        <v>381.8881762783099</v>
       </c>
       <c r="D55">
-        <v>592.1951434567853</v>
+        <v>592.5861762783099</v>
       </c>
       <c r="E55">
-        <v>115.361</v>
+        <v>123.4980000000001</v>
       </c>
       <c r="F55">
-        <v>431.261</v>
+        <v>439.3980000000001</v>
       </c>
       <c r="G55">
         <v>228.7</v>
@@ -5791,28 +5791,28 @@
         <v>194.1</v>
       </c>
       <c r="M55">
-        <v>23.0724635</v>
+        <v>23.507793</v>
       </c>
       <c r="N55">
-        <v>171.0275365</v>
+        <v>170.592207</v>
       </c>
       <c r="O55">
-        <v>42.6542676031</v>
+        <v>42.5456964258</v>
       </c>
       <c r="P55">
-        <v>128.3732688969</v>
+        <v>128.0465105742</v>
       </c>
       <c r="Q55">
-        <v>188.9732688969</v>
+        <v>188.6465105742</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09106067957969893</v>
+        <v>0.09191170619979974</v>
       </c>
       <c r="T55">
-        <v>1.045281283595818</v>
+        <v>1.064935478055421</v>
       </c>
       <c r="U55">
         <v>0.0535</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>8.412625725900487</v>
+        <v>8.256836360606034</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.06396421885190788</v>
+        <v>0.06384665530135726</v>
       </c>
       <c r="C56">
-        <v>381.8881762783099</v>
+        <v>374.1427258474027</v>
       </c>
       <c r="D56">
-        <v>592.5861762783099</v>
+        <v>592.9777258474028</v>
       </c>
       <c r="E56">
-        <v>123.4980000000001</v>
+        <v>131.6350000000001</v>
       </c>
       <c r="F56">
-        <v>439.3980000000001</v>
+        <v>447.5350000000001</v>
       </c>
       <c r="G56">
         <v>228.7</v>
@@ -5873,28 +5873,28 @@
         <v>194.1</v>
       </c>
       <c r="M56">
-        <v>23.507793</v>
+        <v>23.9431225</v>
       </c>
       <c r="N56">
-        <v>170.592207</v>
+        <v>170.1568775</v>
       </c>
       <c r="O56">
-        <v>42.5456964258</v>
+        <v>42.4371252485</v>
       </c>
       <c r="P56">
-        <v>128.0465105742</v>
+        <v>127.7197522515</v>
       </c>
       <c r="Q56">
-        <v>188.6465105742</v>
+        <v>188.3197522515</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09191170619979974</v>
+        <v>0.09280055622523838</v>
       </c>
       <c r="T56">
-        <v>1.064935478055421</v>
+        <v>1.085463192268785</v>
       </c>
       <c r="U56">
         <v>0.0535</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>8.256836360606034</v>
+        <v>8.106712063140467</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.06384665530135726</v>
+        <v>0.06372909175080665</v>
       </c>
       <c r="C57">
-        <v>374.1427258474027</v>
+        <v>366.3977931890592</v>
       </c>
       <c r="D57">
-        <v>592.9777258474028</v>
+        <v>593.3697931890594</v>
       </c>
       <c r="E57">
-        <v>131.6350000000001</v>
+        <v>139.7720000000001</v>
       </c>
       <c r="F57">
-        <v>447.5350000000001</v>
+        <v>455.6720000000001</v>
       </c>
       <c r="G57">
         <v>228.7</v>
@@ -5955,28 +5955,28 @@
         <v>194.1</v>
       </c>
       <c r="M57">
-        <v>23.9431225</v>
+        <v>24.378452</v>
       </c>
       <c r="N57">
-        <v>170.1568775</v>
+        <v>169.721548</v>
       </c>
       <c r="O57">
-        <v>42.4371252485</v>
+        <v>42.3285540712</v>
       </c>
       <c r="P57">
-        <v>127.7197522515</v>
+        <v>127.3929939288</v>
       </c>
       <c r="Q57">
-        <v>188.3197522515</v>
+        <v>187.9929939288</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09280055622523838</v>
+        <v>0.09372980852456059</v>
       </c>
       <c r="T57">
-        <v>1.085463192268785</v>
+        <v>1.106923984400938</v>
       </c>
       <c r="U57">
         <v>0.0535</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>8.106712063140467</v>
+        <v>7.961949347727246</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.06372909175080665</v>
+        <v>0.06361152820025605</v>
       </c>
       <c r="C58">
-        <v>366.3977931890592</v>
+        <v>358.6533793309878</v>
       </c>
       <c r="D58">
-        <v>593.3697931890594</v>
+        <v>593.7623793309879</v>
       </c>
       <c r="E58">
-        <v>139.7720000000001</v>
+        <v>147.9090000000001</v>
       </c>
       <c r="F58">
-        <v>455.6720000000001</v>
+        <v>463.8090000000001</v>
       </c>
       <c r="G58">
         <v>228.7</v>
@@ -6037,28 +6037,28 @@
         <v>194.1</v>
       </c>
       <c r="M58">
-        <v>24.378452</v>
+        <v>24.8137815</v>
       </c>
       <c r="N58">
-        <v>169.721548</v>
+        <v>169.2862185</v>
       </c>
       <c r="O58">
-        <v>42.3285540712</v>
+        <v>42.2199828939</v>
       </c>
       <c r="P58">
-        <v>127.3929939288</v>
+        <v>127.0662356061</v>
       </c>
       <c r="Q58">
-        <v>187.9929939288</v>
+        <v>187.6662356061</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09372980852456059</v>
+        <v>0.09470228186106058</v>
       </c>
       <c r="T58">
-        <v>1.106923984400938</v>
+        <v>1.12938295291133</v>
       </c>
       <c r="U58">
         <v>0.0535</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>7.961949347727246</v>
+        <v>7.822266025837294</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.06361152820025605</v>
+        <v>0.06349396464970543</v>
       </c>
       <c r="C59">
-        <v>358.6533793309878</v>
+        <v>350.9094853036182</v>
       </c>
       <c r="D59">
-        <v>593.7623793309879</v>
+        <v>594.1554853036182</v>
       </c>
       <c r="E59">
-        <v>147.9090000000001</v>
+        <v>156.0460000000001</v>
       </c>
       <c r="F59">
-        <v>463.8090000000001</v>
+        <v>471.9460000000001</v>
       </c>
       <c r="G59">
         <v>228.7</v>
@@ -6119,28 +6119,28 @@
         <v>194.1</v>
       </c>
       <c r="M59">
-        <v>24.8137815</v>
+        <v>25.249111</v>
       </c>
       <c r="N59">
-        <v>169.2862185</v>
+        <v>168.850889</v>
       </c>
       <c r="O59">
-        <v>42.2199828939</v>
+        <v>42.1114117166</v>
       </c>
       <c r="P59">
-        <v>127.0662356061</v>
+        <v>126.7394772834</v>
       </c>
       <c r="Q59">
-        <v>187.6662356061</v>
+        <v>187.3394772834</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.09470228186106058</v>
+        <v>0.09572106345167961</v>
       </c>
       <c r="T59">
-        <v>1.12938295291133</v>
+        <v>1.152911396112693</v>
       </c>
       <c r="U59">
         <v>0.0535</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>7.822266025837294</v>
+        <v>7.68739937021941</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.06349396464970543</v>
+        <v>0.06373068429915482</v>
       </c>
       <c r="C60">
-        <v>350.9094853036183</v>
+        <v>341.9814786725063</v>
       </c>
       <c r="D60">
-        <v>594.1554853036182</v>
+        <v>593.3644786725064</v>
       </c>
       <c r="E60">
-        <v>156.046</v>
+        <v>164.183</v>
       </c>
       <c r="F60">
-        <v>471.946</v>
+        <v>480.083</v>
       </c>
       <c r="G60">
         <v>228.7</v>
@@ -6201,45 +6201,45 @@
         <v>194.1</v>
       </c>
       <c r="M60">
-        <v>25.249111</v>
+        <v>26.0685069</v>
       </c>
       <c r="N60">
-        <v>168.850889</v>
+        <v>168.0314931</v>
       </c>
       <c r="O60">
-        <v>42.1114117166</v>
+        <v>41.90705437913999</v>
       </c>
       <c r="P60">
-        <v>126.7394772834</v>
+        <v>126.12443872086</v>
       </c>
       <c r="Q60">
-        <v>187.3394772834</v>
+        <v>186.72443872086</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.09572106345167961</v>
+        <v>0.09678954170525565</v>
       </c>
       <c r="T60">
-        <v>1.152911396112693</v>
+        <v>1.177587568250708</v>
       </c>
       <c r="U60">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V60">
         <v>0.2494</v>
       </c>
       <c r="W60">
-        <v>0.04015709999999999</v>
+        <v>0.04075757999999999</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y60">
-        <v>7.687399370219411</v>
+        <v>7.445765909976224</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.06373068429915482</v>
+        <v>0.0636191255486042</v>
       </c>
       <c r="C61">
-        <v>341.9814786725063</v>
+        <v>334.2169934063554</v>
       </c>
       <c r="D61">
-        <v>593.3644786725064</v>
+        <v>593.7369934063555</v>
       </c>
       <c r="E61">
-        <v>164.183</v>
+        <v>172.3200000000001</v>
       </c>
       <c r="F61">
-        <v>480.083</v>
+        <v>488.22</v>
       </c>
       <c r="G61">
         <v>228.7</v>
@@ -6283,28 +6283,28 @@
         <v>194.1</v>
       </c>
       <c r="M61">
-        <v>26.0685069</v>
+        <v>26.510346</v>
       </c>
       <c r="N61">
-        <v>168.0314931</v>
+        <v>167.589654</v>
       </c>
       <c r="O61">
-        <v>41.90705437913999</v>
+        <v>41.7968597076</v>
       </c>
       <c r="P61">
-        <v>126.12443872086</v>
+        <v>125.7927942924</v>
       </c>
       <c r="Q61">
-        <v>186.72443872086</v>
+        <v>186.3927942924</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.09678954170525565</v>
+        <v>0.09791144387151052</v>
       </c>
       <c r="T61">
-        <v>1.177587568250708</v>
+        <v>1.203497548995624</v>
       </c>
       <c r="U61">
         <v>0.0543</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>7.445765909976224</v>
+        <v>7.321669811476621</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.0636191255486042</v>
+        <v>0.06350756679805358</v>
       </c>
       <c r="C62">
-        <v>334.2169934063554</v>
+        <v>326.4529761641758</v>
       </c>
       <c r="D62">
-        <v>593.7369934063555</v>
+        <v>594.1099761641759</v>
       </c>
       <c r="E62">
-        <v>172.3200000000001</v>
+        <v>180.4570000000001</v>
       </c>
       <c r="F62">
-        <v>488.22</v>
+        <v>496.357</v>
       </c>
       <c r="G62">
         <v>228.7</v>
@@ -6365,28 +6365,28 @@
         <v>194.1</v>
       </c>
       <c r="M62">
-        <v>26.510346</v>
+        <v>26.9521851</v>
       </c>
       <c r="N62">
-        <v>167.589654</v>
+        <v>167.1478149</v>
       </c>
       <c r="O62">
-        <v>41.7968597076</v>
+        <v>41.68666503606</v>
       </c>
       <c r="P62">
-        <v>125.7927942924</v>
+        <v>125.46114986394</v>
       </c>
       <c r="Q62">
-        <v>186.3927942924</v>
+        <v>186.06114986394</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.09791144387151052</v>
+        <v>0.0990908794821887</v>
       </c>
       <c r="T62">
-        <v>1.203497548995624</v>
+        <v>1.230736246701818</v>
       </c>
       <c r="U62">
         <v>0.0543</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>7.321669811476621</v>
+        <v>7.201642437517988</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.06350756679805358</v>
+        <v>0.06339600804750298</v>
       </c>
       <c r="C63">
-        <v>326.4529761641758</v>
+        <v>318.6894278285532</v>
       </c>
       <c r="D63">
-        <v>594.1099761641759</v>
+        <v>594.4834278285533</v>
       </c>
       <c r="E63">
-        <v>180.4570000000001</v>
+        <v>188.5940000000001</v>
       </c>
       <c r="F63">
-        <v>496.357</v>
+        <v>504.494</v>
       </c>
       <c r="G63">
         <v>228.7</v>
@@ -6447,28 +6447,28 @@
         <v>194.1</v>
       </c>
       <c r="M63">
-        <v>26.9521851</v>
+        <v>27.3940242</v>
       </c>
       <c r="N63">
-        <v>167.1478149</v>
+        <v>166.7059758</v>
       </c>
       <c r="O63">
-        <v>41.68666503606</v>
+        <v>41.57647036452001</v>
       </c>
       <c r="P63">
-        <v>125.46114986394</v>
+        <v>125.12950543548</v>
       </c>
       <c r="Q63">
-        <v>186.06114986394</v>
+        <v>185.72950543548</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.0990908794821887</v>
+        <v>0.1003323906513236</v>
       </c>
       <c r="T63">
-        <v>1.230736246701818</v>
+        <v>1.259408560076758</v>
       </c>
       <c r="U63">
         <v>0.0543</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>7.201642437517988</v>
+        <v>7.085486914332214</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.06339600804750298</v>
+        <v>0.06328444929695237</v>
       </c>
       <c r="C64">
-        <v>318.6894278285532</v>
+        <v>310.9263492842938</v>
       </c>
       <c r="D64">
-        <v>594.4834278285533</v>
+        <v>594.8573492842938</v>
       </c>
       <c r="E64">
-        <v>188.5940000000001</v>
+        <v>196.7310000000001</v>
       </c>
       <c r="F64">
-        <v>504.494</v>
+        <v>512.6310000000001</v>
       </c>
       <c r="G64">
         <v>228.7</v>
@@ -6529,28 +6529,28 @@
         <v>194.1</v>
       </c>
       <c r="M64">
-        <v>27.3940242</v>
+        <v>27.83586330000001</v>
       </c>
       <c r="N64">
-        <v>166.7059758</v>
+        <v>166.2641367</v>
       </c>
       <c r="O64">
-        <v>41.57647036452001</v>
+        <v>41.46627569298</v>
       </c>
       <c r="P64">
-        <v>125.12950543548</v>
+        <v>124.79786100702</v>
       </c>
       <c r="Q64">
-        <v>185.72950543548</v>
+        <v>185.39786100702</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1003323906513236</v>
+        <v>0.1016410105323037</v>
       </c>
       <c r="T64">
-        <v>1.259408560076758</v>
+        <v>1.289630728228723</v>
       </c>
       <c r="U64">
         <v>0.0543</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>7.085486914332214</v>
+        <v>6.973018868072971</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.06328444929695237</v>
+        <v>0.06317289054640175</v>
       </c>
       <c r="C65">
-        <v>310.9263492842938</v>
+        <v>303.1637414184313</v>
       </c>
       <c r="D65">
-        <v>594.8573492842938</v>
+        <v>595.2317414184314</v>
       </c>
       <c r="E65">
-        <v>196.7310000000001</v>
+        <v>204.8680000000001</v>
       </c>
       <c r="F65">
-        <v>512.6310000000001</v>
+        <v>520.768</v>
       </c>
       <c r="G65">
         <v>228.7</v>
@@ -6611,28 +6611,28 @@
         <v>194.1</v>
       </c>
       <c r="M65">
-        <v>27.83586330000001</v>
+        <v>28.2777024</v>
       </c>
       <c r="N65">
-        <v>166.2641367</v>
+        <v>165.8222976</v>
       </c>
       <c r="O65">
-        <v>41.46627569298</v>
+        <v>41.35608102144</v>
       </c>
       <c r="P65">
-        <v>124.79786100702</v>
+        <v>124.46621657856</v>
       </c>
       <c r="Q65">
-        <v>185.39786100702</v>
+        <v>185.06621657856</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1016410105323037</v>
+        <v>0.1030223315177827</v>
       </c>
       <c r="T65">
-        <v>1.289630728228723</v>
+        <v>1.321531905722463</v>
       </c>
       <c r="U65">
         <v>0.0543</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>6.973018868072971</v>
+        <v>6.864065448259331</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.06317289054640175</v>
+        <v>0.06306133179585113</v>
       </c>
       <c r="C66">
-        <v>303.1637414184313</v>
+        <v>295.4016051202344</v>
       </c>
       <c r="D66">
-        <v>595.2317414184314</v>
+        <v>595.6066051202345</v>
       </c>
       <c r="E66">
-        <v>204.8680000000001</v>
+        <v>213.0050000000001</v>
       </c>
       <c r="F66">
-        <v>520.768</v>
+        <v>528.9050000000001</v>
       </c>
       <c r="G66">
         <v>228.7</v>
@@ -6693,28 +6693,28 @@
         <v>194.1</v>
       </c>
       <c r="M66">
-        <v>28.2777024</v>
+        <v>28.71954150000001</v>
       </c>
       <c r="N66">
-        <v>165.8222976</v>
+        <v>165.3804585</v>
       </c>
       <c r="O66">
-        <v>41.35608102144</v>
+        <v>41.2458863499</v>
       </c>
       <c r="P66">
-        <v>124.46621657856</v>
+        <v>124.1345721501</v>
       </c>
       <c r="Q66">
-        <v>185.06621657856</v>
+        <v>184.7345721501</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1030223315177827</v>
+        <v>0.1044825851310033</v>
       </c>
       <c r="T66">
-        <v>1.321531905722463</v>
+        <v>1.355256007644417</v>
       </c>
       <c r="U66">
         <v>0.0543</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>6.864065448259331</v>
+        <v>6.758464441363033</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.06306133179585113</v>
+        <v>0.06294977304530053</v>
       </c>
       <c r="C67">
-        <v>295.4016051202344</v>
+        <v>287.6399412812128</v>
       </c>
       <c r="D67">
-        <v>595.6066051202345</v>
+        <v>595.9819412812128</v>
       </c>
       <c r="E67">
-        <v>213.0050000000001</v>
+        <v>221.1420000000001</v>
       </c>
       <c r="F67">
-        <v>528.9050000000001</v>
+        <v>537.042</v>
       </c>
       <c r="G67">
         <v>228.7</v>
@@ -6775,28 +6775,28 @@
         <v>194.1</v>
       </c>
       <c r="M67">
-        <v>28.71954150000001</v>
+        <v>29.1613806</v>
       </c>
       <c r="N67">
-        <v>165.3804585</v>
+        <v>164.9386194</v>
       </c>
       <c r="O67">
-        <v>41.2458863499</v>
+        <v>41.13569167836</v>
       </c>
       <c r="P67">
-        <v>124.1345721501</v>
+        <v>123.80292772164</v>
       </c>
       <c r="Q67">
-        <v>184.7345721501</v>
+        <v>184.40292772164</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1044825851310033</v>
+        <v>0.1060287360155898</v>
       </c>
       <c r="T67">
-        <v>1.355256007644417</v>
+        <v>1.390963880267663</v>
       </c>
       <c r="U67">
         <v>0.0543</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>6.758464441363033</v>
+        <v>6.656063464978746</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.06294977304530053</v>
+        <v>0.06283821429474991</v>
       </c>
       <c r="C68">
-        <v>287.6399412812128</v>
+        <v>279.8787507951249</v>
       </c>
       <c r="D68">
-        <v>595.9819412812128</v>
+        <v>596.357750795125</v>
       </c>
       <c r="E68">
-        <v>221.1420000000001</v>
+        <v>229.2790000000001</v>
       </c>
       <c r="F68">
-        <v>537.042</v>
+        <v>545.1790000000001</v>
       </c>
       <c r="G68">
         <v>228.7</v>
@@ -6857,28 +6857,28 @@
         <v>194.1</v>
       </c>
       <c r="M68">
-        <v>29.1613806</v>
+        <v>29.6032197</v>
       </c>
       <c r="N68">
-        <v>164.9386194</v>
+        <v>164.4967803</v>
       </c>
       <c r="O68">
-        <v>41.13569167836</v>
+        <v>41.02549700682</v>
       </c>
       <c r="P68">
-        <v>123.80292772164</v>
+        <v>123.47128329318</v>
       </c>
       <c r="Q68">
-        <v>184.40292772164</v>
+        <v>184.07128329318</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1060287360155898</v>
+        <v>0.1076685930143937</v>
       </c>
       <c r="T68">
-        <v>1.390963880267663</v>
+        <v>1.428835866383226</v>
       </c>
       <c r="U68">
         <v>0.0543</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>6.656063464978746</v>
+        <v>6.556719234158167</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.06283821429474991</v>
+        <v>0.06272665554419929</v>
       </c>
       <c r="C69">
-        <v>279.8787507951249</v>
+        <v>272.1180345579853</v>
       </c>
       <c r="D69">
-        <v>596.357750795125</v>
+        <v>596.7340345579853</v>
       </c>
       <c r="E69">
-        <v>229.2790000000001</v>
+        <v>237.4160000000001</v>
       </c>
       <c r="F69">
-        <v>545.1790000000001</v>
+        <v>553.316</v>
       </c>
       <c r="G69">
         <v>228.7</v>
@@ -6939,28 +6939,28 @@
         <v>194.1</v>
       </c>
       <c r="M69">
-        <v>29.6032197</v>
+        <v>30.0450588</v>
       </c>
       <c r="N69">
-        <v>164.4967803</v>
+        <v>164.0549412</v>
       </c>
       <c r="O69">
-        <v>41.02549700682</v>
+        <v>40.91530233528</v>
       </c>
       <c r="P69">
-        <v>123.47128329318</v>
+        <v>123.13963886472</v>
       </c>
       <c r="Q69">
-        <v>184.07128329318</v>
+        <v>183.73963886472</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1076685930143937</v>
+        <v>0.1094109410756228</v>
       </c>
       <c r="T69">
-        <v>1.428835866383226</v>
+        <v>1.469074851631012</v>
       </c>
       <c r="U69">
         <v>0.0543</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>6.556719234158167</v>
+        <v>6.460296892479371</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.06272665554419929</v>
+        <v>0.06261509679364868</v>
       </c>
       <c r="C70">
-        <v>272.1180345579853</v>
+        <v>264.3577934680706</v>
       </c>
       <c r="D70">
-        <v>596.7340345579853</v>
+        <v>597.1107934680707</v>
       </c>
       <c r="E70">
-        <v>237.4160000000001</v>
+        <v>245.5530000000001</v>
       </c>
       <c r="F70">
-        <v>553.316</v>
+        <v>561.4530000000001</v>
       </c>
       <c r="G70">
         <v>228.7</v>
@@ -7021,28 +7021,28 @@
         <v>194.1</v>
       </c>
       <c r="M70">
-        <v>30.0450588</v>
+        <v>30.48689790000001</v>
       </c>
       <c r="N70">
-        <v>164.0549412</v>
+        <v>163.6131021</v>
       </c>
       <c r="O70">
-        <v>40.91530233528</v>
+        <v>40.80510766374</v>
       </c>
       <c r="P70">
-        <v>123.13963886472</v>
+        <v>122.80799443626</v>
       </c>
       <c r="Q70">
-        <v>183.73963886472</v>
+        <v>183.40799443626</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1094109410756228</v>
+        <v>0.1112656986891893</v>
       </c>
       <c r="T70">
-        <v>1.469074851631012</v>
+        <v>1.511909900443172</v>
       </c>
       <c r="U70">
         <v>0.0543</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>6.460296892479371</v>
+        <v>6.366669401284017</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.06261509679364868</v>
+        <v>0.06250353804309808</v>
       </c>
       <c r="C71">
-        <v>264.3577934680706</v>
+        <v>256.5980284259289</v>
       </c>
       <c r="D71">
-        <v>597.1107934680707</v>
+        <v>597.4880284259289</v>
       </c>
       <c r="E71">
-        <v>245.5530000000001</v>
+        <v>253.6900000000001</v>
       </c>
       <c r="F71">
-        <v>561.4530000000001</v>
+        <v>569.59</v>
       </c>
       <c r="G71">
         <v>228.7</v>
@@ -7103,28 +7103,28 @@
         <v>194.1</v>
       </c>
       <c r="M71">
-        <v>30.48689790000001</v>
+        <v>30.928737</v>
       </c>
       <c r="N71">
-        <v>163.6131021</v>
+        <v>163.171263</v>
       </c>
       <c r="O71">
-        <v>40.80510766374</v>
+        <v>40.6949129922</v>
       </c>
       <c r="P71">
-        <v>122.80799443626</v>
+        <v>122.4763500078</v>
       </c>
       <c r="Q71">
-        <v>183.40799443626</v>
+        <v>183.0763500078</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1112656986891893</v>
+        <v>0.113244106810327</v>
       </c>
       <c r="T71">
-        <v>1.511909900443172</v>
+        <v>1.557600619176142</v>
       </c>
       <c r="U71">
         <v>0.0543</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>6.366669401284017</v>
+        <v>6.275716981265674</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.06250353804309808</v>
+        <v>0.06239197929254747</v>
       </c>
       <c r="C72">
-        <v>256.5980284259289</v>
+        <v>248.8387403343834</v>
       </c>
       <c r="D72">
-        <v>597.4880284259289</v>
+        <v>597.8657403343835</v>
       </c>
       <c r="E72">
-        <v>253.6900000000001</v>
+        <v>261.8270000000001</v>
       </c>
       <c r="F72">
-        <v>569.59</v>
+        <v>577.7270000000001</v>
       </c>
       <c r="G72">
         <v>228.7</v>
@@ -7185,28 +7185,28 @@
         <v>194.1</v>
       </c>
       <c r="M72">
-        <v>30.928737</v>
+        <v>31.3705761</v>
       </c>
       <c r="N72">
-        <v>163.171263</v>
+        <v>162.7294239</v>
       </c>
       <c r="O72">
-        <v>40.6949129922</v>
+        <v>40.58471832066</v>
       </c>
       <c r="P72">
-        <v>122.4763500078</v>
+        <v>122.14470557934</v>
       </c>
       <c r="Q72">
-        <v>183.0763500078</v>
+        <v>182.74470557934</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.113244106810327</v>
+        <v>0.1153589568708534</v>
       </c>
       <c r="T72">
-        <v>1.557600619176142</v>
+        <v>1.606442421959662</v>
       </c>
       <c r="U72">
         <v>0.0543</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>6.275716981265674</v>
+        <v>6.187326601247849</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.06239197929254747</v>
+        <v>0.06282085254199686</v>
       </c>
       <c r="C73">
-        <v>248.8387403343835</v>
+        <v>239.2522801969089</v>
       </c>
       <c r="D73">
-        <v>597.8657403343835</v>
+        <v>596.416280196909</v>
       </c>
       <c r="E73">
-        <v>261.827</v>
+        <v>269.9640000000001</v>
       </c>
       <c r="F73">
-        <v>577.727</v>
+        <v>585.864</v>
       </c>
       <c r="G73">
         <v>228.7</v>
@@ -7267,45 +7267,45 @@
         <v>194.1</v>
       </c>
       <c r="M73">
-        <v>31.3705761</v>
+        <v>32.3982792</v>
       </c>
       <c r="N73">
-        <v>162.7294239</v>
+        <v>161.7017208</v>
       </c>
       <c r="O73">
-        <v>40.58471832066</v>
+        <v>40.32840916751999</v>
       </c>
       <c r="P73">
-        <v>122.14470557934</v>
+        <v>121.37331163248</v>
       </c>
       <c r="Q73">
-        <v>182.74470557934</v>
+        <v>181.97331163248</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1153589568708533</v>
+        <v>0.1176248676499888</v>
       </c>
       <c r="T73">
-        <v>1.606442421959662</v>
+        <v>1.658772924942004</v>
       </c>
       <c r="U73">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V73">
         <v>0.2494</v>
       </c>
       <c r="W73">
-        <v>0.04075757999999999</v>
+        <v>0.04150818</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y73">
-        <v>6.187326601247849</v>
+        <v>5.991058932537379</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.06282085254199686</v>
+        <v>0.06271679979144625</v>
       </c>
       <c r="C74">
-        <v>239.2522801969089</v>
+        <v>231.4663004969916</v>
       </c>
       <c r="D74">
-        <v>596.416280196909</v>
+        <v>596.7673004969917</v>
       </c>
       <c r="E74">
-        <v>269.9640000000001</v>
+        <v>278.101</v>
       </c>
       <c r="F74">
-        <v>585.864</v>
+        <v>594.001</v>
       </c>
       <c r="G74">
         <v>228.7</v>
@@ -7349,28 +7349,28 @@
         <v>194.1</v>
       </c>
       <c r="M74">
-        <v>32.3982792</v>
+        <v>32.8482553</v>
       </c>
       <c r="N74">
-        <v>161.7017208</v>
+        <v>161.2517447</v>
       </c>
       <c r="O74">
-        <v>40.32840916751999</v>
+        <v>40.21618512818</v>
       </c>
       <c r="P74">
-        <v>121.37331163248</v>
+        <v>121.03555957182</v>
       </c>
       <c r="Q74">
-        <v>181.97331163248</v>
+        <v>181.63555957182</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1176248676499888</v>
+        <v>0.1200586236720231</v>
       </c>
       <c r="T74">
-        <v>1.658772924942004</v>
+        <v>1.714979761478594</v>
       </c>
       <c r="U74">
         <v>0.0553</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>5.991058932537379</v>
+        <v>5.908989632091663</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.06271679979144625</v>
+        <v>0.06261274704089563</v>
       </c>
       <c r="C75">
-        <v>231.4663004969916</v>
+        <v>223.6807342258022</v>
       </c>
       <c r="D75">
-        <v>596.7673004969917</v>
+        <v>597.1187342258023</v>
       </c>
       <c r="E75">
-        <v>278.101</v>
+        <v>286.2380000000001</v>
       </c>
       <c r="F75">
-        <v>594.001</v>
+        <v>602.138</v>
       </c>
       <c r="G75">
         <v>228.7</v>
@@ -7431,28 +7431,28 @@
         <v>194.1</v>
       </c>
       <c r="M75">
-        <v>32.8482553</v>
+        <v>33.29823140000001</v>
       </c>
       <c r="N75">
-        <v>161.2517447</v>
+        <v>160.8017686</v>
       </c>
       <c r="O75">
-        <v>40.21618512818</v>
+        <v>40.10396108884</v>
       </c>
       <c r="P75">
-        <v>121.03555957182</v>
+        <v>120.69780751116</v>
       </c>
       <c r="Q75">
-        <v>181.63555957182</v>
+        <v>181.29780751116</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1200586236720231</v>
+        <v>0.1226795916957524</v>
       </c>
       <c r="T75">
-        <v>1.714979761478594</v>
+        <v>1.775510200825691</v>
       </c>
       <c r="U75">
         <v>0.0553</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>5.908989632091663</v>
+        <v>5.82913842084718</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.06261274704089563</v>
+        <v>0.06250869429034502</v>
       </c>
       <c r="C76">
-        <v>223.6807342258022</v>
+        <v>215.8955821141703</v>
       </c>
       <c r="D76">
-        <v>597.1187342258023</v>
+        <v>597.4705821141704</v>
       </c>
       <c r="E76">
-        <v>286.2380000000001</v>
+        <v>294.3750000000001</v>
       </c>
       <c r="F76">
-        <v>602.138</v>
+        <v>610.2750000000001</v>
       </c>
       <c r="G76">
         <v>228.7</v>
@@ -7513,28 +7513,28 @@
         <v>194.1</v>
       </c>
       <c r="M76">
-        <v>33.29823140000001</v>
+        <v>33.74820750000001</v>
       </c>
       <c r="N76">
-        <v>160.8017686</v>
+        <v>160.3517925</v>
       </c>
       <c r="O76">
-        <v>40.10396108884</v>
+        <v>39.9917370495</v>
       </c>
       <c r="P76">
-        <v>120.69780751116</v>
+        <v>120.3600554505</v>
       </c>
       <c r="Q76">
-        <v>181.29780751116</v>
+        <v>180.9600554505</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1226795916957524</v>
+        <v>0.1255102371613801</v>
       </c>
       <c r="T76">
-        <v>1.775510200825691</v>
+        <v>1.840883075320556</v>
       </c>
       <c r="U76">
         <v>0.0553</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>5.82913842084718</v>
+        <v>5.751416575235884</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.06250869429034502</v>
+        <v>0.0624046415397944</v>
       </c>
       <c r="C77">
-        <v>215.8955821141703</v>
+        <v>208.1108448946493</v>
       </c>
       <c r="D77">
-        <v>597.4705821141704</v>
+        <v>597.8228448946493</v>
       </c>
       <c r="E77">
-        <v>294.3750000000001</v>
+        <v>302.5120000000001</v>
       </c>
       <c r="F77">
-        <v>610.2750000000001</v>
+        <v>618.412</v>
       </c>
       <c r="G77">
         <v>228.7</v>
@@ -7595,28 +7595,28 @@
         <v>194.1</v>
       </c>
       <c r="M77">
-        <v>33.74820750000001</v>
+        <v>34.1981836</v>
       </c>
       <c r="N77">
-        <v>160.3517925</v>
+        <v>159.9018164</v>
       </c>
       <c r="O77">
-        <v>39.9917370495</v>
+        <v>39.87951301016</v>
       </c>
       <c r="P77">
-        <v>120.3600554505</v>
+        <v>120.02230338984</v>
       </c>
       <c r="Q77">
-        <v>180.9600554505</v>
+        <v>180.62230338984</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1255102371613801</v>
+        <v>0.1285767697491434</v>
       </c>
       <c r="T77">
-        <v>1.840883075320556</v>
+        <v>1.91170368935666</v>
       </c>
       <c r="U77">
         <v>0.0553</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>5.751416575235884</v>
+        <v>5.675740041351202</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.0624046415397944</v>
+        <v>0.06230058878924379</v>
       </c>
       <c r="C78">
-        <v>208.1108448946493</v>
+        <v>200.3265233015208</v>
       </c>
       <c r="D78">
-        <v>597.8228448946493</v>
+        <v>598.1755233015209</v>
       </c>
       <c r="E78">
-        <v>302.5120000000001</v>
+        <v>310.6490000000001</v>
       </c>
       <c r="F78">
-        <v>618.412</v>
+        <v>626.5490000000001</v>
       </c>
       <c r="G78">
         <v>228.7</v>
@@ -7677,28 +7677,28 @@
         <v>194.1</v>
       </c>
       <c r="M78">
-        <v>34.1981836</v>
+        <v>34.64815970000001</v>
       </c>
       <c r="N78">
-        <v>159.9018164</v>
+        <v>159.4518403</v>
       </c>
       <c r="O78">
-        <v>39.87951301016</v>
+        <v>39.76728897082</v>
       </c>
       <c r="P78">
-        <v>120.02230338984</v>
+        <v>119.68455132918</v>
       </c>
       <c r="Q78">
-        <v>180.62230338984</v>
+        <v>180.28455132918</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1285767697491434</v>
+        <v>0.1319099573445382</v>
       </c>
       <c r="T78">
-        <v>1.91170368935666</v>
+        <v>1.988682617656772</v>
       </c>
       <c r="U78">
         <v>0.0553</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>5.675740041351202</v>
+        <v>5.602029131723263</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.06230058878924379</v>
+        <v>0.06219653603869318</v>
       </c>
       <c r="C79">
-        <v>200.3265233015208</v>
+        <v>192.5426180708004</v>
       </c>
       <c r="D79">
-        <v>598.1755233015209</v>
+        <v>598.5286180708005</v>
       </c>
       <c r="E79">
-        <v>310.6490000000001</v>
+        <v>318.7860000000001</v>
       </c>
       <c r="F79">
-        <v>626.5490000000001</v>
+        <v>634.686</v>
       </c>
       <c r="G79">
         <v>228.7</v>
@@ -7759,28 +7759,28 @@
         <v>194.1</v>
       </c>
       <c r="M79">
-        <v>34.64815970000001</v>
+        <v>35.0981358</v>
       </c>
       <c r="N79">
-        <v>159.4518403</v>
+        <v>159.0018642</v>
       </c>
       <c r="O79">
-        <v>39.76728897082</v>
+        <v>39.65506493148</v>
       </c>
       <c r="P79">
-        <v>119.68455132918</v>
+        <v>119.34679926852</v>
       </c>
       <c r="Q79">
-        <v>180.28455132918</v>
+        <v>179.94679926852</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1319099573445382</v>
+        <v>0.1355461619940599</v>
       </c>
       <c r="T79">
-        <v>1.988682617656772</v>
+        <v>2.072659630347804</v>
       </c>
       <c r="U79">
         <v>0.0553</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>5.602029131723263</v>
+        <v>5.53020824541912</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.06219653603869318</v>
+        <v>0.06209248328814257</v>
       </c>
       <c r="C80">
-        <v>192.5426180708004</v>
+        <v>184.7591299402427</v>
       </c>
       <c r="D80">
-        <v>598.5286180708005</v>
+        <v>598.8821299402429</v>
       </c>
       <c r="E80">
-        <v>318.7860000000001</v>
+        <v>326.9230000000001</v>
       </c>
       <c r="F80">
-        <v>634.686</v>
+        <v>642.8230000000001</v>
       </c>
       <c r="G80">
         <v>228.7</v>
@@ -7841,28 +7841,28 @@
         <v>194.1</v>
       </c>
       <c r="M80">
-        <v>35.0981358</v>
+        <v>35.54811190000001</v>
       </c>
       <c r="N80">
-        <v>159.0018642</v>
+        <v>158.5518881</v>
       </c>
       <c r="O80">
-        <v>39.65506493148</v>
+        <v>39.54284089214</v>
       </c>
       <c r="P80">
-        <v>119.34679926852</v>
+        <v>119.00904720786</v>
       </c>
       <c r="Q80">
-        <v>179.94679926852</v>
+        <v>179.60904720786</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1355461619940599</v>
+        <v>0.139528671848298</v>
       </c>
       <c r="T80">
-        <v>2.072659630347804</v>
+        <v>2.164634453771316</v>
       </c>
       <c r="U80">
         <v>0.0553</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>5.53020824541912</v>
+        <v>5.460205609401155</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.06209248328814257</v>
+        <v>0.06198843053759195</v>
       </c>
       <c r="C81">
-        <v>184.7591299402427</v>
+        <v>176.9760596493463</v>
       </c>
       <c r="D81">
-        <v>598.8821299402429</v>
+        <v>599.2360596493464</v>
       </c>
       <c r="E81">
-        <v>326.9230000000001</v>
+        <v>335.0600000000001</v>
       </c>
       <c r="F81">
-        <v>642.8230000000001</v>
+        <v>650.96</v>
       </c>
       <c r="G81">
         <v>228.7</v>
@@ -7923,28 +7923,28 @@
         <v>194.1</v>
       </c>
       <c r="M81">
-        <v>35.54811190000001</v>
+        <v>35.998088</v>
       </c>
       <c r="N81">
-        <v>158.5518881</v>
+        <v>158.101912</v>
       </c>
       <c r="O81">
-        <v>39.54284089214</v>
+        <v>39.4306168528</v>
       </c>
       <c r="P81">
-        <v>119.00904720786</v>
+        <v>118.6712951472</v>
       </c>
       <c r="Q81">
-        <v>179.60904720786</v>
+        <v>179.2712951472</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.139528671848298</v>
+        <v>0.1439094326879598</v>
       </c>
       <c r="T81">
-        <v>2.164634453771316</v>
+        <v>2.265806759537178</v>
       </c>
       <c r="U81">
         <v>0.0553</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>5.460205609401155</v>
+        <v>5.391953039283641</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.06198843053759195</v>
+        <v>0.06188437778704134</v>
       </c>
       <c r="C82">
-        <v>176.9760596493463</v>
+        <v>169.1934079393585</v>
       </c>
       <c r="D82">
-        <v>599.2360596493464</v>
+        <v>599.5904079393587</v>
       </c>
       <c r="E82">
-        <v>335.0600000000001</v>
+        <v>343.1970000000001</v>
       </c>
       <c r="F82">
-        <v>650.96</v>
+        <v>659.0970000000001</v>
       </c>
       <c r="G82">
         <v>228.7</v>
@@ -8005,28 +8005,28 @@
         <v>194.1</v>
       </c>
       <c r="M82">
-        <v>35.998088</v>
+        <v>36.4480641</v>
       </c>
       <c r="N82">
-        <v>158.101912</v>
+        <v>157.6519359</v>
       </c>
       <c r="O82">
-        <v>39.4306168528</v>
+        <v>39.31839281346</v>
       </c>
       <c r="P82">
-        <v>118.6712951472</v>
+        <v>118.33354308654</v>
       </c>
       <c r="Q82">
-        <v>179.2712951472</v>
+        <v>178.93354308654</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1439094326879598</v>
+        <v>0.148751326247586</v>
       </c>
       <c r="T82">
-        <v>2.265806759537178</v>
+        <v>2.377628781699447</v>
       </c>
       <c r="U82">
         <v>0.0553</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>5.391953039283641</v>
+        <v>5.325385717811003</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.06188437778704134</v>
+        <v>0.06178032503649072</v>
       </c>
       <c r="C83">
-        <v>169.1934079393585</v>
+        <v>161.4111755532816</v>
       </c>
       <c r="D83">
-        <v>599.5904079393587</v>
+        <v>599.9451755532816</v>
       </c>
       <c r="E83">
-        <v>343.1970000000001</v>
+        <v>351.3340000000001</v>
       </c>
       <c r="F83">
-        <v>659.0970000000001</v>
+        <v>667.234</v>
       </c>
       <c r="G83">
         <v>228.7</v>
@@ -8087,28 +8087,28 @@
         <v>194.1</v>
       </c>
       <c r="M83">
-        <v>36.4480641</v>
+        <v>36.8980402</v>
       </c>
       <c r="N83">
-        <v>157.6519359</v>
+        <v>157.2019598</v>
       </c>
       <c r="O83">
-        <v>39.31839281346</v>
+        <v>39.20616877412</v>
       </c>
       <c r="P83">
-        <v>118.33354308654</v>
+        <v>117.99579102588</v>
       </c>
       <c r="Q83">
-        <v>178.93354308654</v>
+        <v>178.59579102588</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.148751326247586</v>
+        <v>0.1541312079805041</v>
       </c>
       <c r="T83">
-        <v>2.377628781699447</v>
+        <v>2.501875472990857</v>
       </c>
       <c r="U83">
         <v>0.0553</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>5.325385717811003</v>
+        <v>5.260441989545016</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.06178032503649072</v>
+        <v>0.06167627228594011</v>
       </c>
       <c r="C84">
-        <v>161.4111755532816</v>
+        <v>153.6293632358768</v>
       </c>
       <c r="D84">
-        <v>599.9451755532816</v>
+        <v>600.3003632358768</v>
       </c>
       <c r="E84">
-        <v>351.3340000000001</v>
+        <v>359.4710000000001</v>
       </c>
       <c r="F84">
-        <v>667.234</v>
+        <v>675.3710000000001</v>
       </c>
       <c r="G84">
         <v>228.7</v>
@@ -8169,28 +8169,28 @@
         <v>194.1</v>
       </c>
       <c r="M84">
-        <v>36.8980402</v>
+        <v>37.3480163</v>
       </c>
       <c r="N84">
-        <v>157.2019598</v>
+        <v>156.7519837</v>
       </c>
       <c r="O84">
-        <v>39.20616877412</v>
+        <v>39.09394473478</v>
       </c>
       <c r="P84">
-        <v>117.99579102588</v>
+        <v>117.65803896522</v>
       </c>
       <c r="Q84">
-        <v>178.59579102588</v>
+        <v>178.25803896522</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1541312079805041</v>
+        <v>0.1601440169761184</v>
       </c>
       <c r="T84">
-        <v>2.501875472990857</v>
+        <v>2.640739422081256</v>
       </c>
       <c r="U84">
         <v>0.0553</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>5.260441989545016</v>
+        <v>5.197063170393871</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.06167627228594011</v>
+        <v>0.06157221953538951</v>
       </c>
       <c r="C85">
-        <v>153.6293632358768</v>
+        <v>145.8479717336703</v>
       </c>
       <c r="D85">
-        <v>600.3003632358768</v>
+        <v>600.6559717336705</v>
       </c>
       <c r="E85">
-        <v>359.4710000000001</v>
+        <v>367.6080000000002</v>
       </c>
       <c r="F85">
-        <v>675.3710000000001</v>
+        <v>683.5080000000002</v>
       </c>
       <c r="G85">
         <v>228.7</v>
@@ -8251,28 +8251,28 @@
         <v>194.1</v>
       </c>
       <c r="M85">
-        <v>37.3480163</v>
+        <v>37.79799240000001</v>
       </c>
       <c r="N85">
-        <v>156.7519837</v>
+        <v>156.3020076</v>
       </c>
       <c r="O85">
-        <v>39.09394473478</v>
+        <v>38.98172069544</v>
       </c>
       <c r="P85">
-        <v>117.65803896522</v>
+        <v>117.32028690456</v>
       </c>
       <c r="Q85">
-        <v>178.25803896522</v>
+        <v>177.92028690456</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1601440169761184</v>
+        <v>0.1669084270961845</v>
       </c>
       <c r="T85">
-        <v>2.640739422081256</v>
+        <v>2.796961364807955</v>
       </c>
       <c r="U85">
         <v>0.0553</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>5.197063170393871</v>
+        <v>5.135193370746324</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.06157221953538951</v>
+        <v>0.06146816678483889</v>
       </c>
       <c r="C86">
-        <v>145.8479717336704</v>
+        <v>138.0670017949587</v>
       </c>
       <c r="D86">
-        <v>600.6559717336705</v>
+        <v>601.0120017949588</v>
       </c>
       <c r="E86">
-        <v>367.6080000000001</v>
+        <v>375.745</v>
       </c>
       <c r="F86">
-        <v>683.508</v>
+        <v>691.645</v>
       </c>
       <c r="G86">
         <v>228.7</v>
@@ -8333,28 +8333,28 @@
         <v>194.1</v>
       </c>
       <c r="M86">
-        <v>37.79799240000001</v>
+        <v>38.2479685</v>
       </c>
       <c r="N86">
-        <v>156.3020076</v>
+        <v>155.8520315</v>
       </c>
       <c r="O86">
-        <v>38.98172069544</v>
+        <v>38.8694966561</v>
       </c>
       <c r="P86">
-        <v>117.32028690456</v>
+        <v>116.9825348439</v>
       </c>
       <c r="Q86">
-        <v>177.92028690456</v>
+        <v>177.5825348439</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1669084270961844</v>
+        <v>0.1745747585655926</v>
       </c>
       <c r="T86">
-        <v>2.796961364807954</v>
+        <v>2.974012899898212</v>
       </c>
       <c r="U86">
         <v>0.0553</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>5.135193370746325</v>
+        <v>5.074779331090487</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.06146816678483889</v>
+        <v>0.06136411403428828</v>
       </c>
       <c r="C87">
-        <v>138.0670017949587</v>
+        <v>130.2864541698131</v>
       </c>
       <c r="D87">
-        <v>601.0120017949588</v>
+        <v>601.3684541698132</v>
       </c>
       <c r="E87">
-        <v>375.745</v>
+        <v>383.8820000000001</v>
       </c>
       <c r="F87">
-        <v>691.645</v>
+        <v>699.782</v>
       </c>
       <c r="G87">
         <v>228.7</v>
@@ -8415,28 +8415,28 @@
         <v>194.1</v>
       </c>
       <c r="M87">
-        <v>38.2479685</v>
+        <v>38.69794460000001</v>
       </c>
       <c r="N87">
-        <v>155.8520315</v>
+        <v>155.4020554</v>
       </c>
       <c r="O87">
-        <v>38.8694966561</v>
+        <v>38.75727261676</v>
       </c>
       <c r="P87">
-        <v>116.9825348439</v>
+        <v>116.64478278324</v>
       </c>
       <c r="Q87">
-        <v>177.5825348439</v>
+        <v>177.24478278324</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.1745747585655926</v>
+        <v>0.1833362802449163</v>
       </c>
       <c r="T87">
-        <v>2.974012899898212</v>
+        <v>3.176357511429937</v>
       </c>
       <c r="U87">
         <v>0.0553</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>5.074779331090487</v>
+        <v>5.015770269101061</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.06136411403428828</v>
+        <v>0.06126006128373767</v>
       </c>
       <c r="C88">
-        <v>130.2864541698131</v>
+        <v>122.5063296100856</v>
       </c>
       <c r="D88">
-        <v>601.3684541698132</v>
+        <v>601.7253296100855</v>
       </c>
       <c r="E88">
-        <v>383.8820000000001</v>
+        <v>392.019</v>
       </c>
       <c r="F88">
-        <v>699.782</v>
+        <v>707.919</v>
       </c>
       <c r="G88">
         <v>228.7</v>
@@ -8497,28 +8497,28 @@
         <v>194.1</v>
       </c>
       <c r="M88">
-        <v>38.69794460000001</v>
+        <v>39.1479207</v>
       </c>
       <c r="N88">
-        <v>155.4020554</v>
+        <v>154.9520793</v>
       </c>
       <c r="O88">
-        <v>38.75727261676</v>
+        <v>38.64504857742</v>
       </c>
       <c r="P88">
-        <v>116.64478278324</v>
+        <v>116.30703072258</v>
       </c>
       <c r="Q88">
-        <v>177.24478278324</v>
+        <v>176.90703072258</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.1833362802449163</v>
+        <v>0.1934457283364436</v>
       </c>
       <c r="T88">
-        <v>3.176357511429937</v>
+        <v>3.409832063197312</v>
       </c>
       <c r="U88">
         <v>0.0553</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>5.015770269101061</v>
+        <v>4.958117737272314</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.06126006128373767</v>
+        <v>0.06115600853318706</v>
       </c>
       <c r="C89">
-        <v>122.5063296100856</v>
+        <v>114.7266288694136</v>
       </c>
       <c r="D89">
-        <v>601.7253296100855</v>
+        <v>602.0826288694136</v>
       </c>
       <c r="E89">
-        <v>392.019</v>
+        <v>400.1560000000001</v>
       </c>
       <c r="F89">
-        <v>707.919</v>
+        <v>716.056</v>
       </c>
       <c r="G89">
         <v>228.7</v>
@@ -8579,28 +8579,28 @@
         <v>194.1</v>
       </c>
       <c r="M89">
-        <v>39.1479207</v>
+        <v>39.5978968</v>
       </c>
       <c r="N89">
-        <v>154.9520793</v>
+        <v>154.5021032</v>
       </c>
       <c r="O89">
-        <v>38.64504857742</v>
+        <v>38.53282453808</v>
       </c>
       <c r="P89">
-        <v>116.30703072258</v>
+        <v>115.96927866192</v>
       </c>
       <c r="Q89">
-        <v>176.90703072258</v>
+        <v>176.56927866192</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.1934457283364436</v>
+        <v>0.2052400844432255</v>
       </c>
       <c r="T89">
-        <v>3.409832063197312</v>
+        <v>3.682219040259249</v>
       </c>
       <c r="U89">
         <v>0.0553</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>4.958117737272314</v>
+        <v>4.901775490257856</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.06115600853318706</v>
+        <v>0.06105195578263643</v>
       </c>
       <c r="C90">
-        <v>114.7266288694136</v>
+        <v>106.9473527032259</v>
       </c>
       <c r="D90">
-        <v>602.0826288694136</v>
+        <v>602.4403527032259</v>
       </c>
       <c r="E90">
-        <v>400.1560000000001</v>
+        <v>408.2930000000001</v>
       </c>
       <c r="F90">
-        <v>716.056</v>
+        <v>724.1930000000001</v>
       </c>
       <c r="G90">
         <v>228.7</v>
@@ -8661,28 +8661,28 @@
         <v>194.1</v>
       </c>
       <c r="M90">
-        <v>39.5978968</v>
+        <v>40.04787290000001</v>
       </c>
       <c r="N90">
-        <v>154.5021032</v>
+        <v>154.0521271</v>
       </c>
       <c r="O90">
-        <v>38.53282453808</v>
+        <v>38.42060049873999</v>
       </c>
       <c r="P90">
-        <v>115.96927866192</v>
+        <v>115.63152660126</v>
       </c>
       <c r="Q90">
-        <v>176.56927866192</v>
+        <v>176.23152660126</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2052400844432255</v>
+        <v>0.2191788689330586</v>
       </c>
       <c r="T90">
-        <v>3.682219040259249</v>
+        <v>4.004130922241537</v>
       </c>
       <c r="U90">
         <v>0.0553</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>4.901775490257856</v>
+        <v>4.846699361153834</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.06105195578263643</v>
+        <v>0.06094790303208582</v>
       </c>
       <c r="C91">
-        <v>106.9473527032259</v>
+        <v>99.16850186874797</v>
       </c>
       <c r="D91">
-        <v>602.4403527032259</v>
+        <v>602.798501868748</v>
       </c>
       <c r="E91">
-        <v>408.2930000000001</v>
+        <v>416.4300000000001</v>
       </c>
       <c r="F91">
-        <v>724.1930000000001</v>
+        <v>732.33</v>
       </c>
       <c r="G91">
         <v>228.7</v>
@@ -8743,28 +8743,28 @@
         <v>194.1</v>
       </c>
       <c r="M91">
-        <v>40.04787290000001</v>
+        <v>40.497849</v>
       </c>
       <c r="N91">
-        <v>154.0521271</v>
+        <v>153.602151</v>
       </c>
       <c r="O91">
-        <v>38.42060049873999</v>
+        <v>38.3083764594</v>
       </c>
       <c r="P91">
-        <v>115.63152660126</v>
+        <v>115.2937745406</v>
       </c>
       <c r="Q91">
-        <v>176.23152660126</v>
+        <v>175.8937745406</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2191788689330586</v>
+        <v>0.2359054103208583</v>
       </c>
       <c r="T91">
-        <v>4.004130922241537</v>
+        <v>4.390425180620285</v>
       </c>
       <c r="U91">
         <v>0.0553</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>4.846699361153834</v>
+        <v>4.792847146029903</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.06094790303208582</v>
+        <v>0.06084385028153522</v>
       </c>
       <c r="C92">
-        <v>99.16850186874797</v>
+        <v>91.39007712500643</v>
       </c>
       <c r="D92">
-        <v>602.798501868748</v>
+        <v>603.1570771250065</v>
       </c>
       <c r="E92">
-        <v>416.4300000000001</v>
+        <v>424.5670000000001</v>
       </c>
       <c r="F92">
-        <v>732.33</v>
+        <v>740.4670000000001</v>
       </c>
       <c r="G92">
         <v>228.7</v>
@@ -8825,28 +8825,28 @@
         <v>194.1</v>
       </c>
       <c r="M92">
-        <v>40.497849</v>
+        <v>40.94782510000001</v>
       </c>
       <c r="N92">
-        <v>153.602151</v>
+        <v>153.1521749</v>
       </c>
       <c r="O92">
-        <v>38.3083764594</v>
+        <v>38.19615242006</v>
       </c>
       <c r="P92">
-        <v>115.2937745406</v>
+        <v>114.95602247994</v>
       </c>
       <c r="Q92">
-        <v>175.8937745406</v>
+        <v>175.55602247994</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2359054103208583</v>
+        <v>0.2563489609059469</v>
       </c>
       <c r="T92">
-        <v>4.390425180620285</v>
+        <v>4.862562607527642</v>
       </c>
       <c r="U92">
         <v>0.0553</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>4.792847146029903</v>
+        <v>4.74017849607353</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.06084385028153522</v>
+        <v>0.0607397975309846</v>
       </c>
       <c r="C93">
-        <v>91.39007712500643</v>
+        <v>83.61207923283541</v>
       </c>
       <c r="D93">
-        <v>603.1570771250065</v>
+        <v>603.5160792328355</v>
       </c>
       <c r="E93">
-        <v>424.5670000000001</v>
+        <v>432.7040000000001</v>
       </c>
       <c r="F93">
-        <v>740.4670000000001</v>
+        <v>748.604</v>
       </c>
       <c r="G93">
         <v>228.7</v>
@@ -8907,28 +8907,28 @@
         <v>194.1</v>
       </c>
       <c r="M93">
-        <v>40.94782510000001</v>
+        <v>41.3978012</v>
       </c>
       <c r="N93">
-        <v>153.1521749</v>
+        <v>152.7021988</v>
       </c>
       <c r="O93">
-        <v>38.19615242006</v>
+        <v>38.08392838072</v>
       </c>
       <c r="P93">
-        <v>114.95602247994</v>
+        <v>114.61827041928</v>
       </c>
       <c r="Q93">
-        <v>175.55602247994</v>
+        <v>175.21827041928</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.2563489609059469</v>
+        <v>0.2819033991373077</v>
       </c>
       <c r="T93">
-        <v>4.862562607527642</v>
+        <v>5.45273439116184</v>
       </c>
       <c r="U93">
         <v>0.0553</v>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>4.74017849607353</v>
+        <v>4.688654816768384</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.0607397975309846</v>
+        <v>0.06063574478043399</v>
       </c>
       <c r="C94">
-        <v>83.61207923283541</v>
+        <v>75.83450895488124</v>
       </c>
       <c r="D94">
-        <v>603.5160792328355</v>
+        <v>603.8755089548814</v>
       </c>
       <c r="E94">
-        <v>432.7040000000001</v>
+        <v>440.8410000000001</v>
       </c>
       <c r="F94">
-        <v>748.604</v>
+        <v>756.7410000000001</v>
       </c>
       <c r="G94">
         <v>228.7</v>
@@ -8989,28 +8989,28 @@
         <v>194.1</v>
       </c>
       <c r="M94">
-        <v>41.3978012</v>
+        <v>41.8477773</v>
       </c>
       <c r="N94">
-        <v>152.7021988</v>
+        <v>152.2522227</v>
       </c>
       <c r="O94">
-        <v>38.08392838072</v>
+        <v>37.97170434138</v>
       </c>
       <c r="P94">
-        <v>114.61827041928</v>
+        <v>114.28051835862</v>
       </c>
       <c r="Q94">
-        <v>175.21827041928</v>
+        <v>174.88051835862</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.2819033991373077</v>
+        <v>0.3147591054347715</v>
       </c>
       <c r="T94">
-        <v>5.45273439116184</v>
+        <v>6.211526684405808</v>
       </c>
       <c r="U94">
         <v>0.0553</v>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>4.688654816768384</v>
+        <v>4.638239173577326</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.06063574478043399</v>
+        <v>0.06053169202988337</v>
       </c>
       <c r="C95">
-        <v>75.83450895488124</v>
+        <v>68.05736705560878</v>
       </c>
       <c r="D95">
-        <v>603.8755089548814</v>
+        <v>604.2353670556089</v>
       </c>
       <c r="E95">
-        <v>440.8410000000001</v>
+        <v>448.9780000000001</v>
       </c>
       <c r="F95">
-        <v>756.7410000000001</v>
+        <v>764.878</v>
       </c>
       <c r="G95">
         <v>228.7</v>
@@ -9071,28 +9071,28 @@
         <v>194.1</v>
       </c>
       <c r="M95">
-        <v>41.8477773</v>
+        <v>42.2977534</v>
       </c>
       <c r="N95">
-        <v>152.2522227</v>
+        <v>151.8022466</v>
       </c>
       <c r="O95">
-        <v>37.97170434138</v>
+        <v>37.85948030204</v>
       </c>
       <c r="P95">
-        <v>114.28051835862</v>
+        <v>113.94276629796</v>
       </c>
       <c r="Q95">
-        <v>174.88051835862</v>
+        <v>174.54276629796</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3147591054347715</v>
+        <v>0.3585667138313899</v>
       </c>
       <c r="T95">
-        <v>6.211526684405808</v>
+        <v>7.223249742064432</v>
       </c>
       <c r="U95">
         <v>0.0553</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>4.638239173577326</v>
+        <v>4.588896203645652</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.06053169202988337</v>
+        <v>0.06042763927933276</v>
       </c>
       <c r="C96">
-        <v>68.05736705560878</v>
+        <v>60.28065430130528</v>
       </c>
       <c r="D96">
-        <v>604.2353670556089</v>
+        <v>604.5956543013053</v>
       </c>
       <c r="E96">
-        <v>448.9780000000001</v>
+        <v>457.1150000000001</v>
       </c>
       <c r="F96">
-        <v>764.878</v>
+        <v>773.0150000000001</v>
       </c>
       <c r="G96">
         <v>228.7</v>
@@ -9153,28 +9153,28 @@
         <v>194.1</v>
       </c>
       <c r="M96">
-        <v>42.2977534</v>
+        <v>42.74772950000001</v>
       </c>
       <c r="N96">
-        <v>151.8022466</v>
+        <v>151.3522705</v>
       </c>
       <c r="O96">
-        <v>37.85948030204</v>
+        <v>37.7472562627</v>
       </c>
       <c r="P96">
-        <v>113.94276629796</v>
+        <v>113.6050142373</v>
       </c>
       <c r="Q96">
-        <v>174.54276629796</v>
+        <v>174.2050142373</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.3585667138313899</v>
+        <v>0.4198973655866558</v>
       </c>
       <c r="T96">
-        <v>7.223249742064432</v>
+        <v>8.639662022786508</v>
       </c>
       <c r="U96">
         <v>0.0553</v>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>4.588896203645652</v>
+        <v>4.54059203308096</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.06042763927933276</v>
+        <v>0.06212502652878216</v>
       </c>
       <c r="C97">
-        <v>60.28065430130528</v>
+        <v>46.31952170866737</v>
       </c>
       <c r="D97">
-        <v>604.5956543013053</v>
+        <v>598.7715217086676</v>
       </c>
       <c r="E97">
-        <v>457.1150000000001</v>
+        <v>465.2520000000002</v>
       </c>
       <c r="F97">
-        <v>773.0150000000001</v>
+        <v>781.1520000000002</v>
       </c>
       <c r="G97">
         <v>228.7</v>
@@ -9235,45 +9235,45 @@
         <v>194.1</v>
       </c>
       <c r="M97">
-        <v>42.74772950000001</v>
+        <v>45.15058560000001</v>
       </c>
       <c r="N97">
-        <v>151.3522705</v>
+        <v>148.9494144</v>
       </c>
       <c r="O97">
-        <v>37.7472562627</v>
+        <v>37.14798395135999</v>
       </c>
       <c r="P97">
-        <v>113.6050142373</v>
+        <v>111.80143044864</v>
       </c>
       <c r="Q97">
-        <v>174.2050142373</v>
+        <v>172.40143044864</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.4198973655866558</v>
+        <v>0.5118933432195547</v>
       </c>
       <c r="T97">
-        <v>8.639662022786508</v>
+        <v>10.76428044386962</v>
       </c>
       <c r="U97">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V97">
         <v>0.2494</v>
       </c>
       <c r="W97">
-        <v>0.04150818</v>
+        <v>0.04338468</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y97">
-        <v>4.54059203308096</v>
+        <v>4.298947564480756</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.06212502652878216</v>
+        <v>0.06203973877823155</v>
       </c>
       <c r="C98">
-        <v>46.31952170866748</v>
+        <v>38.47248522377004</v>
       </c>
       <c r="D98">
-        <v>598.7715217086676</v>
+        <v>599.0614852237701</v>
       </c>
       <c r="E98">
-        <v>465.2520000000001</v>
+        <v>473.389</v>
       </c>
       <c r="F98">
-        <v>781.152</v>
+        <v>789.289</v>
       </c>
       <c r="G98">
         <v>228.7</v>
@@ -9317,28 +9317,28 @@
         <v>194.1</v>
       </c>
       <c r="M98">
-        <v>45.15058560000001</v>
+        <v>45.62090420000001</v>
       </c>
       <c r="N98">
-        <v>148.9494144</v>
+        <v>148.4790958</v>
       </c>
       <c r="O98">
-        <v>37.14798395136</v>
+        <v>37.03068649252</v>
       </c>
       <c r="P98">
-        <v>111.80143044864</v>
+        <v>111.44840930748</v>
       </c>
       <c r="Q98">
-        <v>172.40143044864</v>
+        <v>172.04840930748</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.5118933432195534</v>
+        <v>0.6652199726077175</v>
       </c>
       <c r="T98">
-        <v>10.76428044386959</v>
+        <v>14.30531114567477</v>
       </c>
       <c r="U98">
         <v>0.0578</v>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>4.298947564480757</v>
+        <v>4.254628517424255</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.06203973877823155</v>
+        <v>0.06195445102768093</v>
       </c>
       <c r="C99">
-        <v>38.47248522377004</v>
+        <v>30.62572971274369</v>
       </c>
       <c r="D99">
-        <v>599.0614852237701</v>
+        <v>599.3517297127438</v>
       </c>
       <c r="E99">
-        <v>473.389</v>
+        <v>481.5260000000001</v>
       </c>
       <c r="F99">
-        <v>789.289</v>
+        <v>797.426</v>
       </c>
       <c r="G99">
         <v>228.7</v>
@@ -9399,28 +9399,28 @@
         <v>194.1</v>
       </c>
       <c r="M99">
-        <v>45.62090420000001</v>
+        <v>46.0912228</v>
       </c>
       <c r="N99">
-        <v>148.4790958</v>
+        <v>148.0087772</v>
       </c>
       <c r="O99">
-        <v>37.03068649252</v>
+        <v>36.91338903368</v>
       </c>
       <c r="P99">
-        <v>111.44840930748</v>
+        <v>111.09538816632</v>
       </c>
       <c r="Q99">
-        <v>172.04840930748</v>
+        <v>171.69538816632</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.6652199726077175</v>
+        <v>0.9718732313840457</v>
       </c>
       <c r="T99">
-        <v>14.30531114567477</v>
+        <v>21.38737254928512</v>
       </c>
       <c r="U99">
         <v>0.0578</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>4.254628517424255</v>
+        <v>4.211213940715845</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.06195445102768093</v>
+        <v>0.06186916327713032</v>
       </c>
       <c r="C100">
-        <v>30.62572971274369</v>
+        <v>22.77925558418076</v>
       </c>
       <c r="D100">
-        <v>599.3517297127438</v>
+        <v>599.6422555841807</v>
       </c>
       <c r="E100">
-        <v>481.5260000000001</v>
+        <v>489.663</v>
       </c>
       <c r="F100">
-        <v>797.426</v>
+        <v>805.563</v>
       </c>
       <c r="G100">
         <v>228.7</v>
@@ -9481,28 +9481,28 @@
         <v>194.1</v>
       </c>
       <c r="M100">
-        <v>46.0912228</v>
+        <v>46.5615414</v>
       </c>
       <c r="N100">
-        <v>148.0087772</v>
+        <v>147.5384586</v>
       </c>
       <c r="O100">
-        <v>36.91338903368</v>
+        <v>36.79609157484</v>
       </c>
       <c r="P100">
-        <v>111.09538816632</v>
+        <v>110.74236702516</v>
       </c>
       <c r="Q100">
-        <v>171.69538816632</v>
+        <v>171.34236702516</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>0.9718732313840457</v>
+        <v>1.89183300771303</v>
       </c>
       <c r="T100">
-        <v>21.38737254928512</v>
+        <v>42.63355676011616</v>
       </c>
       <c r="U100">
         <v>0.0578</v>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>4.211213940715845</v>
+        <v>4.168676426163159</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.06186916327713032</v>
-      </c>
-      <c r="C101">
-        <v>22.77925558418076</v>
-      </c>
-      <c r="D101">
-        <v>599.6422555841807</v>
-      </c>
-      <c r="E101">
-        <v>489.663</v>
-      </c>
-      <c r="F101">
-        <v>805.563</v>
-      </c>
-      <c r="G101">
-        <v>228.7</v>
-      </c>
-      <c r="H101">
-        <v>497.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>254.7</v>
-      </c>
-      <c r="K101">
-        <v>60.6</v>
-      </c>
-      <c r="L101">
-        <v>194.1</v>
-      </c>
-      <c r="M101">
-        <v>46.5615414</v>
-      </c>
-      <c r="N101">
-        <v>147.5384586</v>
-      </c>
-      <c r="O101">
-        <v>36.79609157484</v>
-      </c>
-      <c r="P101">
-        <v>110.74236702516</v>
-      </c>
-      <c r="Q101">
-        <v>171.34236702516</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>1.89183300771303</v>
-      </c>
-      <c r="T101">
-        <v>42.63355676011616</v>
-      </c>
-      <c r="U101">
-        <v>0.0578</v>
-      </c>
-      <c r="V101">
-        <v>0.2494</v>
-      </c>
-      <c r="W101">
-        <v>0.04338468</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Baa2/BBB</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>4.168676426163159</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
